--- a/BOND_EQT/reg_HS Tech.xlsx
+++ b/BOND_EQT/reg_HS Tech.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c060ac0a7f9c7ae2/main/CRAMC_Desktop/EU/BOND_EQT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{2773DC52-B2E1-442E-8E9F-479DDE4DEB2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8BCB6FC-3F1A-4A83-B7BE-55B77E4F66C0}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="8_{2773DC52-B2E1-442E-8E9F-479DDE4DEB2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCCE39A4-F6E1-4578-B0D1-DC69D144E713}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="480" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="480" windowWidth="16440" windowHeight="28440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -130,21 +130,21 @@
       <tp t="e">
         <v>#N/A</v>
         <stp/>
-        <stp>BDH|14049501234159561198</stp>
+        <stp>BDH|12960302437871177505</stp>
         <tr r="C1" s="2"/>
+      </tp>
+    </main>
+    <main first="bofaddin.rtdserver">
+      <tp t="e">
+        <v>#N/A</v>
+        <stp/>
+        <stp>BDH|3251234060618079766</stp>
+        <tr r="D1" s="2"/>
       </tp>
       <tp t="e">
         <v>#N/A</v>
         <stp/>
-        <stp>BDH|12379947721503079785</stp>
-        <tr r="D1" s="2"/>
-      </tp>
-    </main>
-    <main first="bofaddin.rtdserver">
-      <tp t="s">
-        <v>#N/A N/A</v>
-        <stp/>
-        <stp>BDH|5880802984461791641</stp>
+        <stp>BDH|279743278180750885</stp>
         <tr r="A1" s="2"/>
       </tp>
     </main>
@@ -419,7 +419,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C1872"/>
+  <dimension ref="A1:C1900"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -20666,7 +20666,7 @@
       </c>
     </row>
     <row r="1841" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1841">
+      <c r="A1841" s="1">
         <v>45878</v>
       </c>
       <c r="B1841">
@@ -20677,7 +20677,7 @@
       </c>
     </row>
     <row r="1842" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1842">
+      <c r="A1842" s="1">
         <v>45879</v>
       </c>
       <c r="B1842">
@@ -20688,7 +20688,7 @@
       </c>
     </row>
     <row r="1843" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1843">
+      <c r="A1843" s="1">
         <v>45880</v>
       </c>
       <c r="B1843">
@@ -20699,7 +20699,7 @@
       </c>
     </row>
     <row r="1844" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1844">
+      <c r="A1844" s="1">
         <v>45881</v>
       </c>
       <c r="B1844">
@@ -20710,7 +20710,7 @@
       </c>
     </row>
     <row r="1845" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1845">
+      <c r="A1845" s="1">
         <v>45882</v>
       </c>
       <c r="B1845">
@@ -20721,7 +20721,7 @@
       </c>
     </row>
     <row r="1846" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1846">
+      <c r="A1846" s="1">
         <v>45883</v>
       </c>
       <c r="B1846">
@@ -20732,7 +20732,7 @@
       </c>
     </row>
     <row r="1847" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1847">
+      <c r="A1847" s="1">
         <v>45884</v>
       </c>
       <c r="B1847">
@@ -20743,7 +20743,7 @@
       </c>
     </row>
     <row r="1848" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1848">
+      <c r="A1848" s="1">
         <v>45885</v>
       </c>
       <c r="B1848">
@@ -20754,7 +20754,7 @@
       </c>
     </row>
     <row r="1849" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1849">
+      <c r="A1849" s="1">
         <v>45886</v>
       </c>
       <c r="B1849">
@@ -20765,7 +20765,7 @@
       </c>
     </row>
     <row r="1850" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1850">
+      <c r="A1850" s="1">
         <v>45887</v>
       </c>
       <c r="B1850">
@@ -20776,7 +20776,7 @@
       </c>
     </row>
     <row r="1851" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1851">
+      <c r="A1851" s="1">
         <v>45888</v>
       </c>
       <c r="B1851">
@@ -20787,7 +20787,7 @@
       </c>
     </row>
     <row r="1852" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1852">
+      <c r="A1852" s="1">
         <v>45889</v>
       </c>
       <c r="B1852">
@@ -20798,7 +20798,7 @@
       </c>
     </row>
     <row r="1853" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1853">
+      <c r="A1853" s="1">
         <v>45890</v>
       </c>
       <c r="B1853">
@@ -20809,7 +20809,7 @@
       </c>
     </row>
     <row r="1854" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1854">
+      <c r="A1854" s="1">
         <v>45891</v>
       </c>
       <c r="B1854">
@@ -20820,7 +20820,7 @@
       </c>
     </row>
     <row r="1855" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1855">
+      <c r="A1855" s="1">
         <v>45892</v>
       </c>
       <c r="B1855">
@@ -20831,7 +20831,7 @@
       </c>
     </row>
     <row r="1856" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1856">
+      <c r="A1856" s="1">
         <v>45893</v>
       </c>
       <c r="B1856">
@@ -20842,7 +20842,7 @@
       </c>
     </row>
     <row r="1857" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1857">
+      <c r="A1857" s="1">
         <v>45894</v>
       </c>
       <c r="B1857">
@@ -20853,7 +20853,7 @@
       </c>
     </row>
     <row r="1858" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1858">
+      <c r="A1858" s="1">
         <v>45895</v>
       </c>
       <c r="B1858">
@@ -20864,7 +20864,7 @@
       </c>
     </row>
     <row r="1859" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1859">
+      <c r="A1859" s="1">
         <v>45896</v>
       </c>
       <c r="B1859">
@@ -20875,7 +20875,7 @@
       </c>
     </row>
     <row r="1860" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1860">
+      <c r="A1860" s="1">
         <v>45897</v>
       </c>
       <c r="B1860">
@@ -20886,7 +20886,7 @@
       </c>
     </row>
     <row r="1861" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1861">
+      <c r="A1861" s="1">
         <v>45898</v>
       </c>
       <c r="B1861">
@@ -20897,7 +20897,7 @@
       </c>
     </row>
     <row r="1862" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1862">
+      <c r="A1862" s="1">
         <v>45899</v>
       </c>
       <c r="B1862">
@@ -20908,7 +20908,7 @@
       </c>
     </row>
     <row r="1863" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1863">
+      <c r="A1863" s="1">
         <v>45900</v>
       </c>
       <c r="B1863">
@@ -20919,7 +20919,7 @@
       </c>
     </row>
     <row r="1864" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1864">
+      <c r="A1864" s="1">
         <v>45901</v>
       </c>
       <c r="B1864">
@@ -20930,7 +20930,7 @@
       </c>
     </row>
     <row r="1865" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1865">
+      <c r="A1865" s="1">
         <v>45902</v>
       </c>
       <c r="B1865">
@@ -20941,7 +20941,7 @@
       </c>
     </row>
     <row r="1866" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1866">
+      <c r="A1866" s="1">
         <v>45903</v>
       </c>
       <c r="B1866">
@@ -20952,7 +20952,7 @@
       </c>
     </row>
     <row r="1867" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1867">
+      <c r="A1867" s="1">
         <v>45904</v>
       </c>
       <c r="B1867">
@@ -20963,7 +20963,7 @@
       </c>
     </row>
     <row r="1868" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1868">
+      <c r="A1868" s="1">
         <v>45905</v>
       </c>
       <c r="B1868">
@@ -20974,7 +20974,7 @@
       </c>
     </row>
     <row r="1869" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1869">
+      <c r="A1869" s="1">
         <v>45906</v>
       </c>
       <c r="B1869">
@@ -20985,7 +20985,7 @@
       </c>
     </row>
     <row r="1870" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1870">
+      <c r="A1870" s="1">
         <v>45907</v>
       </c>
       <c r="B1870">
@@ -20996,7 +20996,7 @@
       </c>
     </row>
     <row r="1871" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1871">
+      <c r="A1871" s="1">
         <v>45908</v>
       </c>
       <c r="B1871">
@@ -21007,7 +21007,7 @@
       </c>
     </row>
     <row r="1872" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1872">
+      <c r="A1872" s="1">
         <v>45909</v>
       </c>
       <c r="B1872">
@@ -21015,6 +21015,314 @@
       </c>
       <c r="C1872">
         <v>-2.2865000000000002</v>
+      </c>
+    </row>
+    <row r="1873" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1873" s="1">
+        <v>45910</v>
+      </c>
+      <c r="B1873">
+        <v>5902.69</v>
+      </c>
+      <c r="C1873">
+        <v>-2.2214</v>
+      </c>
+    </row>
+    <row r="1874" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1874" s="1">
+        <v>45911</v>
+      </c>
+      <c r="B1874">
+        <v>5888.77</v>
+      </c>
+      <c r="C1874">
+        <v>-2.2136</v>
+      </c>
+    </row>
+    <row r="1875" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1875" s="1">
+        <v>45912</v>
+      </c>
+      <c r="B1875">
+        <v>5989.27</v>
+      </c>
+      <c r="C1875">
+        <v>-2.2623000000000002</v>
+      </c>
+    </row>
+    <row r="1876" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1876" s="1">
+        <v>45913</v>
+      </c>
+      <c r="B1876">
+        <v>5989.27</v>
+      </c>
+      <c r="C1876">
+        <v>-2.2623000000000002</v>
+      </c>
+    </row>
+    <row r="1877" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1877" s="1">
+        <v>45914</v>
+      </c>
+      <c r="B1877">
+        <v>5989.27</v>
+      </c>
+      <c r="C1877">
+        <v>-2.2623000000000002</v>
+      </c>
+    </row>
+    <row r="1878" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1878" s="1">
+        <v>45915</v>
+      </c>
+      <c r="B1878">
+        <v>6043.61</v>
+      </c>
+      <c r="C1878">
+        <v>-2.2364999999999995</v>
+      </c>
+    </row>
+    <row r="1879" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1879" s="1">
+        <v>45916</v>
+      </c>
+      <c r="B1879">
+        <v>6077.66</v>
+      </c>
+      <c r="C1879">
+        <v>-2.2408999999999999</v>
+      </c>
+    </row>
+    <row r="1880" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1880" s="1">
+        <v>45917</v>
+      </c>
+      <c r="B1880">
+        <v>6334.24</v>
+      </c>
+      <c r="C1880">
+        <v>-2.3162000000000003</v>
+      </c>
+    </row>
+    <row r="1881" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1881" s="1">
+        <v>45918</v>
+      </c>
+      <c r="B1881">
+        <v>6271.22</v>
+      </c>
+      <c r="C1881">
+        <v>-2.3224</v>
+      </c>
+    </row>
+    <row r="1882" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1882" s="1">
+        <v>45919</v>
+      </c>
+      <c r="B1882">
+        <v>6294.42</v>
+      </c>
+      <c r="C1882">
+        <v>-2.3293999999999997</v>
+      </c>
+    </row>
+    <row r="1883" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1883" s="1">
+        <v>45920</v>
+      </c>
+      <c r="B1883">
+        <v>6294.42</v>
+      </c>
+      <c r="C1883">
+        <v>-2.3293999999999997</v>
+      </c>
+    </row>
+    <row r="1884" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1884" s="1">
+        <v>45921</v>
+      </c>
+      <c r="B1884">
+        <v>6294.42</v>
+      </c>
+      <c r="C1884">
+        <v>-2.3293999999999997</v>
+      </c>
+    </row>
+    <row r="1885" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1885" s="1">
+        <v>45922</v>
+      </c>
+      <c r="B1885">
+        <v>6257.91</v>
+      </c>
+      <c r="C1885">
+        <v>-2.3547000000000002</v>
+      </c>
+    </row>
+    <row r="1886" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1886" s="1">
+        <v>45923</v>
+      </c>
+      <c r="B1886">
+        <v>6167.06</v>
+      </c>
+      <c r="C1886">
+        <v>-2.3040999999999996</v>
+      </c>
+    </row>
+    <row r="1887" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1887" s="1">
+        <v>45924</v>
+      </c>
+      <c r="B1887">
+        <v>6323.15</v>
+      </c>
+      <c r="C1887">
+        <v>-2.2416</v>
+      </c>
+    </row>
+    <row r="1888" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1888" s="1">
+        <v>45925</v>
+      </c>
+      <c r="B1888">
+        <v>6379.19</v>
+      </c>
+      <c r="C1888">
+        <v>-2.2768000000000006</v>
+      </c>
+    </row>
+    <row r="1889" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1889" s="1">
+        <v>45926</v>
+      </c>
+      <c r="B1889">
+        <v>6195.11</v>
+      </c>
+      <c r="C1889">
+        <v>-2.2875000000000005</v>
+      </c>
+    </row>
+    <row r="1890" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1890" s="1">
+        <v>45927</v>
+      </c>
+      <c r="B1890">
+        <v>6195.11</v>
+      </c>
+      <c r="C1890">
+        <v>-2.2875000000000005</v>
+      </c>
+    </row>
+    <row r="1891" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1891" s="1">
+        <v>45928</v>
+      </c>
+      <c r="B1891">
+        <v>6195.11</v>
+      </c>
+      <c r="C1891">
+        <v>-2.2875000000000005</v>
+      </c>
+    </row>
+    <row r="1892" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1892" s="1">
+        <v>45929</v>
+      </c>
+      <c r="B1892">
+        <v>6324.25</v>
+      </c>
+      <c r="C1892">
+        <v>-2.2416999999999998</v>
+      </c>
+    </row>
+    <row r="1893" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1893" s="1">
+        <v>45930</v>
+      </c>
+      <c r="B1893">
+        <v>6465.66</v>
+      </c>
+      <c r="C1893">
+        <v>-2.2792999999999997</v>
+      </c>
+    </row>
+    <row r="1894" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1894" s="1">
+        <v>45931</v>
+      </c>
+      <c r="B1894">
+        <v>6465.66</v>
+      </c>
+      <c r="C1894">
+        <v>-2.2270999999999996</v>
+      </c>
+    </row>
+    <row r="1895" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1895" s="1">
+        <v>45932</v>
+      </c>
+      <c r="B1895">
+        <v>6682.86</v>
+      </c>
+      <c r="C1895">
+        <v>-2.2117</v>
+      </c>
+    </row>
+    <row r="1896" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1896" s="1">
+        <v>45933</v>
+      </c>
+      <c r="B1896">
+        <v>6622.85</v>
+      </c>
+      <c r="C1896">
+        <v>-2.2482000000000002</v>
+      </c>
+    </row>
+    <row r="1897" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1897" s="1">
+        <v>45934</v>
+      </c>
+      <c r="B1897">
+        <v>6622.85</v>
+      </c>
+      <c r="C1897">
+        <v>-2.2482000000000002</v>
+      </c>
+    </row>
+    <row r="1898" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1898" s="1">
+        <v>45935</v>
+      </c>
+      <c r="B1898">
+        <v>6622.85</v>
+      </c>
+      <c r="C1898">
+        <v>-2.2482000000000002</v>
+      </c>
+    </row>
+    <row r="1899" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1899" s="1">
+        <v>45936</v>
+      </c>
+      <c r="B1899">
+        <v>6550.3</v>
+      </c>
+      <c r="C1899">
+        <v>-2.2810000000000001</v>
+      </c>
+    </row>
+    <row r="1900" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1900" s="1">
+        <v>45937</v>
+      </c>
+      <c r="B1900">
+        <v>6550.3</v>
+      </c>
+      <c r="C1900">
+        <v>-2.2520000000000002</v>
       </c>
     </row>
   </sheetData>
@@ -21024,26 +21332,28 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C44AB31A-70CE-4A6E-A84E-7592026AAEFA}">
-  <dimension ref="A1:E1873"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E1899"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="0" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="5" max="5" width="9.140625" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" cm="1">
-        <f t="array" ref="A1:B1871">_xll.BDH("HSTECH Index", "PX_LAST", "7/27/2020", "9/9/2025", "Days", "C", "BEST_FPERIOD_OVERRIDE", "1BF")</f>
+        <f t="array" ref="A1:B1899">_xll.BDH("HSTECH Index", "PX_LAST", "7/27/2020", "10/7/2025", "Days", "C", "BEST_FPERIOD_OVERRIDE", "1BF")</f>
         <v>44039</v>
       </c>
       <c r="B1">
         <v>6774.78</v>
       </c>
       <c r="C1" cm="1">
-        <f t="array" ref="C1:C1871">_xll.BDH("GCNY10YR Index", "PX_LAST", "7/27/2020", "9/9/2025", "Days", "C", "Dates", "Hide")</f>
+        <f t="array" ref="C1:C1899">_xll.BDH("GCNY10YR Index", "PX_LAST", "7/27/2020", "10/7/2025", "Days", "C", "Dates", "Hide")</f>
         <v>2.8959999999999999</v>
       </c>
       <c r="D1" cm="1">
-        <f t="array" ref="D1:D1871">_xll.BDH("USGG10YR Index", "PX_LAST", "7/27/2020", "9/9/2025", "Days", "C", "Dates", "Hide")</f>
+        <f t="array" ref="D1:D1899">_xll.BDH("USGG10YR Index", "PX_LAST", "7/27/2020", "10/7/2025", "Days", "C", "Dates", "Hide")</f>
         <v>0.61509999999999998</v>
       </c>
       <c r="E1">
@@ -54473,7 +54783,7 @@
         <v>4.2343000000000002</v>
       </c>
       <c r="E1858">
-        <f t="shared" ref="E1858:E1871" si="29">C1858-D1858</f>
+        <f t="shared" ref="E1858:E1899" si="29">C1858-D1858</f>
         <v>-2.4643000000000002</v>
       </c>
     </row>
@@ -54712,10 +55022,508 @@
       </c>
     </row>
     <row r="1872" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1872" s="1"/>
-    </row>
-    <row r="1873" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1873" s="1"/>
+      <c r="A1872" s="1">
+        <v>45910</v>
+      </c>
+      <c r="B1872">
+        <v>5902.69</v>
+      </c>
+      <c r="C1872">
+        <v>1.8240000000000001</v>
+      </c>
+      <c r="D1872">
+        <v>4.0453999999999999</v>
+      </c>
+      <c r="E1872">
+        <f t="shared" si="29"/>
+        <v>-2.2214</v>
+      </c>
+    </row>
+    <row r="1873" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1873" s="1">
+        <v>45911</v>
+      </c>
+      <c r="B1873">
+        <v>5888.77</v>
+      </c>
+      <c r="C1873">
+        <v>1.8069999999999999</v>
+      </c>
+      <c r="D1873">
+        <v>4.0206</v>
+      </c>
+      <c r="E1873">
+        <f t="shared" si="29"/>
+        <v>-2.2136</v>
+      </c>
+    </row>
+    <row r="1874" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1874" s="1">
+        <v>45912</v>
+      </c>
+      <c r="B1874">
+        <v>5989.27</v>
+      </c>
+      <c r="C1874">
+        <v>1.802</v>
+      </c>
+      <c r="D1874">
+        <v>4.0643000000000002</v>
+      </c>
+      <c r="E1874">
+        <f t="shared" si="29"/>
+        <v>-2.2623000000000002</v>
+      </c>
+    </row>
+    <row r="1875" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1875" s="1">
+        <v>45913</v>
+      </c>
+      <c r="B1875">
+        <v>5989.27</v>
+      </c>
+      <c r="C1875">
+        <v>1.802</v>
+      </c>
+      <c r="D1875">
+        <v>4.0643000000000002</v>
+      </c>
+      <c r="E1875">
+        <f t="shared" si="29"/>
+        <v>-2.2623000000000002</v>
+      </c>
+    </row>
+    <row r="1876" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1876" s="1">
+        <v>45914</v>
+      </c>
+      <c r="B1876">
+        <v>5989.27</v>
+      </c>
+      <c r="C1876">
+        <v>1.802</v>
+      </c>
+      <c r="D1876">
+        <v>4.0643000000000002</v>
+      </c>
+      <c r="E1876">
+        <f t="shared" si="29"/>
+        <v>-2.2623000000000002</v>
+      </c>
+    </row>
+    <row r="1877" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1877" s="1">
+        <v>45915</v>
+      </c>
+      <c r="B1877">
+        <v>6043.61</v>
+      </c>
+      <c r="C1877">
+        <v>1.8009999999999999</v>
+      </c>
+      <c r="D1877">
+        <v>4.0374999999999996</v>
+      </c>
+      <c r="E1877">
+        <f t="shared" si="29"/>
+        <v>-2.2364999999999995</v>
+      </c>
+    </row>
+    <row r="1878" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1878" s="1">
+        <v>45916</v>
+      </c>
+      <c r="B1878">
+        <v>6077.66</v>
+      </c>
+      <c r="C1878">
+        <v>1.7869999999999999</v>
+      </c>
+      <c r="D1878">
+        <v>4.0278999999999998</v>
+      </c>
+      <c r="E1878">
+        <f t="shared" si="29"/>
+        <v>-2.2408999999999999</v>
+      </c>
+    </row>
+    <row r="1879" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1879" s="1">
+        <v>45917</v>
+      </c>
+      <c r="B1879">
+        <v>6334.24</v>
+      </c>
+      <c r="C1879">
+        <v>1.7709999999999999</v>
+      </c>
+      <c r="D1879">
+        <v>4.0872000000000002</v>
+      </c>
+      <c r="E1879">
+        <f t="shared" si="29"/>
+        <v>-2.3162000000000003</v>
+      </c>
+    </row>
+    <row r="1880" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1880" s="1">
+        <v>45918</v>
+      </c>
+      <c r="B1880">
+        <v>6271.22</v>
+      </c>
+      <c r="C1880">
+        <v>1.782</v>
+      </c>
+      <c r="D1880">
+        <v>4.1044</v>
+      </c>
+      <c r="E1880">
+        <f t="shared" si="29"/>
+        <v>-2.3224</v>
+      </c>
+    </row>
+    <row r="1881" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1881" s="1">
+        <v>45919</v>
+      </c>
+      <c r="B1881">
+        <v>6294.42</v>
+      </c>
+      <c r="C1881">
+        <v>1.798</v>
+      </c>
+      <c r="D1881">
+        <v>4.1273999999999997</v>
+      </c>
+      <c r="E1881">
+        <f t="shared" si="29"/>
+        <v>-2.3293999999999997</v>
+      </c>
+    </row>
+    <row r="1882" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1882" s="1">
+        <v>45920</v>
+      </c>
+      <c r="B1882">
+        <v>6294.42</v>
+      </c>
+      <c r="C1882">
+        <v>1.798</v>
+      </c>
+      <c r="D1882">
+        <v>4.1273999999999997</v>
+      </c>
+      <c r="E1882">
+        <f t="shared" si="29"/>
+        <v>-2.3293999999999997</v>
+      </c>
+    </row>
+    <row r="1883" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1883" s="1">
+        <v>45921</v>
+      </c>
+      <c r="B1883">
+        <v>6294.42</v>
+      </c>
+      <c r="C1883">
+        <v>1.798</v>
+      </c>
+      <c r="D1883">
+        <v>4.1273999999999997</v>
+      </c>
+      <c r="E1883">
+        <f t="shared" si="29"/>
+        <v>-2.3293999999999997</v>
+      </c>
+    </row>
+    <row r="1884" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1884" s="1">
+        <v>45922</v>
+      </c>
+      <c r="B1884">
+        <v>6257.91</v>
+      </c>
+      <c r="C1884">
+        <v>1.792</v>
+      </c>
+      <c r="D1884">
+        <v>4.1467000000000001</v>
+      </c>
+      <c r="E1884">
+        <f t="shared" si="29"/>
+        <v>-2.3547000000000002</v>
+      </c>
+    </row>
+    <row r="1885" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1885" s="1">
+        <v>45923</v>
+      </c>
+      <c r="B1885">
+        <v>6167.06</v>
+      </c>
+      <c r="C1885">
+        <v>1.802</v>
+      </c>
+      <c r="D1885">
+        <v>4.1060999999999996</v>
+      </c>
+      <c r="E1885">
+        <f t="shared" si="29"/>
+        <v>-2.3040999999999996</v>
+      </c>
+    </row>
+    <row r="1886" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1886" s="1">
+        <v>45924</v>
+      </c>
+      <c r="B1886">
+        <v>6323.15</v>
+      </c>
+      <c r="C1886">
+        <v>1.905</v>
+      </c>
+      <c r="D1886">
+        <v>4.1466000000000003</v>
+      </c>
+      <c r="E1886">
+        <f t="shared" si="29"/>
+        <v>-2.2416</v>
+      </c>
+    </row>
+    <row r="1887" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1887" s="1">
+        <v>45925</v>
+      </c>
+      <c r="B1887">
+        <v>6379.19</v>
+      </c>
+      <c r="C1887">
+        <v>1.893</v>
+      </c>
+      <c r="D1887">
+        <v>4.1698000000000004</v>
+      </c>
+      <c r="E1887">
+        <f t="shared" si="29"/>
+        <v>-2.2768000000000006</v>
+      </c>
+    </row>
+    <row r="1888" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1888" s="1">
+        <v>45926</v>
+      </c>
+      <c r="B1888">
+        <v>6195.11</v>
+      </c>
+      <c r="C1888">
+        <v>1.8879999999999999</v>
+      </c>
+      <c r="D1888">
+        <v>4.1755000000000004</v>
+      </c>
+      <c r="E1888">
+        <f t="shared" si="29"/>
+        <v>-2.2875000000000005</v>
+      </c>
+    </row>
+    <row r="1889" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1889" s="1">
+        <v>45927</v>
+      </c>
+      <c r="B1889">
+        <v>6195.11</v>
+      </c>
+      <c r="C1889">
+        <v>1.8879999999999999</v>
+      </c>
+      <c r="D1889">
+        <v>4.1755000000000004</v>
+      </c>
+      <c r="E1889">
+        <f t="shared" si="29"/>
+        <v>-2.2875000000000005</v>
+      </c>
+    </row>
+    <row r="1890" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1890" s="1">
+        <v>45928</v>
+      </c>
+      <c r="B1890">
+        <v>6195.11</v>
+      </c>
+      <c r="C1890">
+        <v>1.8879999999999999</v>
+      </c>
+      <c r="D1890">
+        <v>4.1755000000000004</v>
+      </c>
+      <c r="E1890">
+        <f t="shared" si="29"/>
+        <v>-2.2875000000000005</v>
+      </c>
+    </row>
+    <row r="1891" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1891" s="1">
+        <v>45929</v>
+      </c>
+      <c r="B1891">
+        <v>6324.25</v>
+      </c>
+      <c r="C1891">
+        <v>1.897</v>
+      </c>
+      <c r="D1891">
+        <v>4.1387</v>
+      </c>
+      <c r="E1891">
+        <f t="shared" si="29"/>
+        <v>-2.2416999999999998</v>
+      </c>
+    </row>
+    <row r="1892" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1892" s="1">
+        <v>45930</v>
+      </c>
+      <c r="B1892">
+        <v>6465.66</v>
+      </c>
+      <c r="C1892">
+        <v>1.871</v>
+      </c>
+      <c r="D1892">
+        <v>4.1502999999999997</v>
+      </c>
+      <c r="E1892">
+        <f t="shared" si="29"/>
+        <v>-2.2792999999999997</v>
+      </c>
+    </row>
+    <row r="1893" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1893" s="1">
+        <v>45931</v>
+      </c>
+      <c r="B1893">
+        <v>6465.66</v>
+      </c>
+      <c r="C1893">
+        <v>1.871</v>
+      </c>
+      <c r="D1893">
+        <v>4.0980999999999996</v>
+      </c>
+      <c r="E1893">
+        <f t="shared" si="29"/>
+        <v>-2.2270999999999996</v>
+      </c>
+    </row>
+    <row r="1894" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1894" s="1">
+        <v>45932</v>
+      </c>
+      <c r="B1894">
+        <v>6682.86</v>
+      </c>
+      <c r="C1894">
+        <v>1.871</v>
+      </c>
+      <c r="D1894">
+        <v>4.0827</v>
+      </c>
+      <c r="E1894">
+        <f t="shared" si="29"/>
+        <v>-2.2117</v>
+      </c>
+    </row>
+    <row r="1895" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1895" s="1">
+        <v>45933</v>
+      </c>
+      <c r="B1895">
+        <v>6622.85</v>
+      </c>
+      <c r="C1895">
+        <v>1.871</v>
+      </c>
+      <c r="D1895">
+        <v>4.1192000000000002</v>
+      </c>
+      <c r="E1895">
+        <f t="shared" si="29"/>
+        <v>-2.2482000000000002</v>
+      </c>
+    </row>
+    <row r="1896" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1896" s="1">
+        <v>45934</v>
+      </c>
+      <c r="B1896">
+        <v>6622.85</v>
+      </c>
+      <c r="C1896">
+        <v>1.871</v>
+      </c>
+      <c r="D1896">
+        <v>4.1192000000000002</v>
+      </c>
+      <c r="E1896">
+        <f t="shared" si="29"/>
+        <v>-2.2482000000000002</v>
+      </c>
+    </row>
+    <row r="1897" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1897" s="1">
+        <v>45935</v>
+      </c>
+      <c r="B1897">
+        <v>6622.85</v>
+      </c>
+      <c r="C1897">
+        <v>1.871</v>
+      </c>
+      <c r="D1897">
+        <v>4.1192000000000002</v>
+      </c>
+      <c r="E1897">
+        <f t="shared" si="29"/>
+        <v>-2.2482000000000002</v>
+      </c>
+    </row>
+    <row r="1898" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1898" s="1">
+        <v>45936</v>
+      </c>
+      <c r="B1898">
+        <v>6550.3</v>
+      </c>
+      <c r="C1898">
+        <v>1.871</v>
+      </c>
+      <c r="D1898">
+        <v>4.1520000000000001</v>
+      </c>
+      <c r="E1898">
+        <f t="shared" si="29"/>
+        <v>-2.2810000000000001</v>
+      </c>
+    </row>
+    <row r="1899" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1899" s="1">
+        <v>45937</v>
+      </c>
+      <c r="B1899">
+        <v>6550.3</v>
+      </c>
+      <c r="C1899">
+        <v>1.871</v>
+      </c>
+      <c r="D1899">
+        <v>4.1230000000000002</v>
+      </c>
+      <c r="E1899">
+        <f t="shared" si="29"/>
+        <v>-2.2520000000000002</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C275">

--- a/BOND_EQT/reg_HS Tech.xlsx
+++ b/BOND_EQT/reg_HS Tech.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c060ac0a7f9c7ae2/main/CRAMC_Desktop/EU/BOND_EQT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="8_{2773DC52-B2E1-442E-8E9F-479DDE4DEB2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCCE39A4-F6E1-4578-B0D1-DC69D144E713}"/>
+  <xr:revisionPtr revIDLastSave="51" documentId="8_{2773DC52-B2E1-442E-8E9F-479DDE4DEB2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92A0A9AD-D0EE-4E79-B964-F45C0E181E08}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="480" windowWidth="16440" windowHeight="28440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="480" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -127,33 +127,29 @@
 <volTypes xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <volType type="realTimeData">
     <main first="bofaddin.rtdserver">
-      <tp t="e">
-        <v>#N/A</v>
+      <tp t="s">
+        <v>#N/A N/A</v>
         <stp/>
-        <stp>BDH|12960302437871177505</stp>
+        <stp>BDH|10116834236230611777</stp>
         <tr r="C1" s="2"/>
+      </tp>
+      <tp t="s">
+        <v>#N/A N/A</v>
+        <stp/>
+        <stp>BDH|15235929736366660909</stp>
+        <tr r="D1" s="2"/>
       </tp>
     </main>
     <main first="bofaddin.rtdserver">
-      <tp t="e">
-        <v>#N/A</v>
+      <tp t="s">
+        <v>#N/A N/A</v>
         <stp/>
-        <stp>BDH|3251234060618079766</stp>
-        <tr r="D1" s="2"/>
-      </tp>
-      <tp t="e">
-        <v>#N/A</v>
-        <stp/>
-        <stp>BDH|279743278180750885</stp>
+        <stp>BDH|9838886424443202136</stp>
         <tr r="A1" s="2"/>
       </tp>
     </main>
   </volType>
 </volTypes>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -419,7 +415,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C1900"/>
+  <dimension ref="A1:C1964"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -21325,6 +21321,710 @@
         <v>-2.2520000000000002</v>
       </c>
     </row>
+    <row r="1901" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1901" s="1">
+        <v>45938</v>
+      </c>
+      <c r="B1901">
+        <v>6514.19</v>
+      </c>
+      <c r="C1901">
+        <v>-2.2460999999999998</v>
+      </c>
+    </row>
+    <row r="1902" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1902" s="1">
+        <v>45939</v>
+      </c>
+      <c r="B1902">
+        <v>6471.34</v>
+      </c>
+      <c r="C1902">
+        <v>-2.2873999999999999</v>
+      </c>
+    </row>
+    <row r="1903" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1903" s="1">
+        <v>45940</v>
+      </c>
+      <c r="B1903">
+        <v>6259.75</v>
+      </c>
+      <c r="C1903">
+        <v>-2.1761999999999997</v>
+      </c>
+    </row>
+    <row r="1904" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1904" s="1">
+        <v>45941</v>
+      </c>
+      <c r="B1904">
+        <v>6259.75</v>
+      </c>
+      <c r="C1904">
+        <v>-2.1761999999999997</v>
+      </c>
+    </row>
+    <row r="1905" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1905" s="1">
+        <v>45942</v>
+      </c>
+      <c r="B1905">
+        <v>6259.75</v>
+      </c>
+      <c r="C1905">
+        <v>-2.1761999999999997</v>
+      </c>
+    </row>
+    <row r="1906" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1906" s="1">
+        <v>45943</v>
+      </c>
+      <c r="B1906">
+        <v>6145.51</v>
+      </c>
+      <c r="C1906">
+        <v>-2.1841999999999997</v>
+      </c>
+    </row>
+    <row r="1907" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1907" s="1">
+        <v>45944</v>
+      </c>
+      <c r="B1907">
+        <v>5923.26</v>
+      </c>
+      <c r="C1907">
+        <v>-2.1940999999999997</v>
+      </c>
+    </row>
+    <row r="1908" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1908" s="1">
+        <v>45945</v>
+      </c>
+      <c r="B1908">
+        <v>6075.27</v>
+      </c>
+      <c r="C1908">
+        <v>-2.1841999999999997</v>
+      </c>
+    </row>
+    <row r="1909" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1909" s="1">
+        <v>45946</v>
+      </c>
+      <c r="B1909">
+        <v>6003.56</v>
+      </c>
+      <c r="C1909">
+        <v>-2.1355</v>
+      </c>
+    </row>
+    <row r="1910" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1910" s="1">
+        <v>45947</v>
+      </c>
+      <c r="B1910">
+        <v>5760.38</v>
+      </c>
+      <c r="C1910">
+        <v>-2.1818</v>
+      </c>
+    </row>
+    <row r="1911" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1911" s="1">
+        <v>45948</v>
+      </c>
+      <c r="B1911">
+        <v>5760.38</v>
+      </c>
+      <c r="C1911">
+        <v>-2.1818</v>
+      </c>
+    </row>
+    <row r="1912" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1912" s="1">
+        <v>45949</v>
+      </c>
+      <c r="B1912">
+        <v>5760.38</v>
+      </c>
+      <c r="C1912">
+        <v>-2.1818</v>
+      </c>
+    </row>
+    <row r="1913" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1913" s="1">
+        <v>45950</v>
+      </c>
+      <c r="B1913">
+        <v>5933.17</v>
+      </c>
+      <c r="C1913">
+        <v>-2.133</v>
+      </c>
+    </row>
+    <row r="1914" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1914" s="1">
+        <v>45951</v>
+      </c>
+      <c r="B1914">
+        <v>6007.94</v>
+      </c>
+      <c r="C1914">
+        <v>-2.1236999999999999</v>
+      </c>
+    </row>
+    <row r="1915" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1915" s="1">
+        <v>45952</v>
+      </c>
+      <c r="B1915">
+        <v>5923.09</v>
+      </c>
+      <c r="C1915">
+        <v>-2.1203000000000003</v>
+      </c>
+    </row>
+    <row r="1916" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1916" s="1">
+        <v>45953</v>
+      </c>
+      <c r="B1916">
+        <v>5951.45</v>
+      </c>
+      <c r="C1916">
+        <v>-2.1638999999999999</v>
+      </c>
+    </row>
+    <row r="1917" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1917" s="1">
+        <v>45954</v>
+      </c>
+      <c r="B1917">
+        <v>6059.89</v>
+      </c>
+      <c r="C1917">
+        <v>-2.1497000000000002</v>
+      </c>
+    </row>
+    <row r="1918" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1918" s="1">
+        <v>45955</v>
+      </c>
+      <c r="B1918">
+        <v>6059.89</v>
+      </c>
+      <c r="C1918">
+        <v>-2.1497000000000002</v>
+      </c>
+    </row>
+    <row r="1919" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1919" s="1">
+        <v>45956</v>
+      </c>
+      <c r="B1919">
+        <v>6059.89</v>
+      </c>
+      <c r="C1919">
+        <v>-2.1497000000000002</v>
+      </c>
+    </row>
+    <row r="1920" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1920" s="1">
+        <v>45957</v>
+      </c>
+      <c r="B1920">
+        <v>6171.08</v>
+      </c>
+      <c r="C1920">
+        <v>-2.1694999999999998</v>
+      </c>
+    </row>
+    <row r="1921" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1921" s="1">
+        <v>45958</v>
+      </c>
+      <c r="B1921">
+        <v>6093.44</v>
+      </c>
+      <c r="C1921">
+        <v>-2.1626000000000003</v>
+      </c>
+    </row>
+    <row r="1922" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1922" s="1">
+        <v>45959</v>
+      </c>
+      <c r="B1922">
+        <v>6093.44</v>
+      </c>
+      <c r="C1922">
+        <v>-2.2617000000000003</v>
+      </c>
+    </row>
+    <row r="1923" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1923" s="1">
+        <v>45960</v>
+      </c>
+      <c r="B1923">
+        <v>6051.76</v>
+      </c>
+      <c r="C1923">
+        <v>-2.2870000000000004</v>
+      </c>
+    </row>
+    <row r="1924" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1924" s="1">
+        <v>45961</v>
+      </c>
+      <c r="B1924">
+        <v>5908.08</v>
+      </c>
+      <c r="C1924">
+        <v>-2.2805</v>
+      </c>
+    </row>
+    <row r="1925" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1925" s="1">
+        <v>45962</v>
+      </c>
+      <c r="B1925">
+        <v>5908.08</v>
+      </c>
+      <c r="C1925">
+        <v>-2.2805</v>
+      </c>
+    </row>
+    <row r="1926" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1926" s="1">
+        <v>45963</v>
+      </c>
+      <c r="B1926">
+        <v>5908.08</v>
+      </c>
+      <c r="C1926">
+        <v>-2.2805</v>
+      </c>
+    </row>
+    <row r="1927" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1927" s="1">
+        <v>45964</v>
+      </c>
+      <c r="B1927">
+        <v>5922.48</v>
+      </c>
+      <c r="C1927">
+        <v>-2.3184000000000005</v>
+      </c>
+    </row>
+    <row r="1928" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1928" s="1">
+        <v>45965</v>
+      </c>
+      <c r="B1928">
+        <v>5818.29</v>
+      </c>
+      <c r="C1928">
+        <v>-2.2902000000000005</v>
+      </c>
+    </row>
+    <row r="1929" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1929" s="1">
+        <v>45966</v>
+      </c>
+      <c r="B1929">
+        <v>5785.85</v>
+      </c>
+      <c r="C1929">
+        <v>-2.3620999999999999</v>
+      </c>
+    </row>
+    <row r="1930" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1930" s="1">
+        <v>45967</v>
+      </c>
+      <c r="B1930">
+        <v>5944.22</v>
+      </c>
+      <c r="C1930">
+        <v>-2.2770999999999999</v>
+      </c>
+    </row>
+    <row r="1931" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1931" s="1">
+        <v>45968</v>
+      </c>
+      <c r="B1931">
+        <v>5837.36</v>
+      </c>
+      <c r="C1931">
+        <v>-2.2885999999999997</v>
+      </c>
+    </row>
+    <row r="1932" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1932" s="1">
+        <v>45969</v>
+      </c>
+      <c r="B1932">
+        <v>5837.36</v>
+      </c>
+      <c r="C1932">
+        <v>-2.2885999999999997</v>
+      </c>
+    </row>
+    <row r="1933" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1933" s="1">
+        <v>45970</v>
+      </c>
+      <c r="B1933">
+        <v>5837.36</v>
+      </c>
+      <c r="C1933">
+        <v>-2.2885999999999997</v>
+      </c>
+    </row>
+    <row r="1934" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1934" s="1">
+        <v>45971</v>
+      </c>
+      <c r="B1934">
+        <v>5915.56</v>
+      </c>
+      <c r="C1934">
+        <v>-2.3079999999999998</v>
+      </c>
+    </row>
+    <row r="1935" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1935" s="1">
+        <v>45972</v>
+      </c>
+      <c r="B1935">
+        <v>5924.39</v>
+      </c>
+      <c r="C1935">
+        <v>-2.3049999999999997</v>
+      </c>
+    </row>
+    <row r="1936" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1936" s="1">
+        <v>45973</v>
+      </c>
+      <c r="B1936">
+        <v>5933.99</v>
+      </c>
+      <c r="C1936">
+        <v>-2.2652999999999999</v>
+      </c>
+    </row>
+    <row r="1937" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1937" s="1">
+        <v>45974</v>
+      </c>
+      <c r="B1937">
+        <v>5981.3</v>
+      </c>
+      <c r="C1937">
+        <v>-2.3112000000000004</v>
+      </c>
+    </row>
+    <row r="1938" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1938" s="1">
+        <v>45975</v>
+      </c>
+      <c r="B1938">
+        <v>5812.8</v>
+      </c>
+      <c r="C1938">
+        <v>-2.3403</v>
+      </c>
+    </row>
+    <row r="1939" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1939" s="1">
+        <v>45976</v>
+      </c>
+      <c r="B1939">
+        <v>5812.8</v>
+      </c>
+      <c r="C1939">
+        <v>-2.3403</v>
+      </c>
+    </row>
+    <row r="1940" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1940" s="1">
+        <v>45977</v>
+      </c>
+      <c r="B1940">
+        <v>5812.8</v>
+      </c>
+      <c r="C1940">
+        <v>-2.3403</v>
+      </c>
+    </row>
+    <row r="1941" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1941" s="1">
+        <v>45978</v>
+      </c>
+      <c r="B1941">
+        <v>5756.88</v>
+      </c>
+      <c r="C1941">
+        <v>-2.3316000000000003</v>
+      </c>
+    </row>
+    <row r="1942" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1942" s="1">
+        <v>45979</v>
+      </c>
+      <c r="B1942">
+        <v>5645.73</v>
+      </c>
+      <c r="C1942">
+        <v>-2.3074000000000003</v>
+      </c>
+    </row>
+    <row r="1943" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1943" s="1">
+        <v>45980</v>
+      </c>
+      <c r="B1943">
+        <v>5606.9</v>
+      </c>
+      <c r="C1943">
+        <v>-2.3267000000000002</v>
+      </c>
+    </row>
+    <row r="1944" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1944" s="1">
+        <v>45981</v>
+      </c>
+      <c r="B1944">
+        <v>5574.59</v>
+      </c>
+      <c r="C1944">
+        <v>-2.2735000000000003</v>
+      </c>
+    </row>
+    <row r="1945" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1945" s="1">
+        <v>45982</v>
+      </c>
+      <c r="B1945">
+        <v>5395.49</v>
+      </c>
+      <c r="C1945">
+        <v>-2.2492999999999999</v>
+      </c>
+    </row>
+    <row r="1946" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1946" s="1">
+        <v>45983</v>
+      </c>
+      <c r="B1946">
+        <v>5395.49</v>
+      </c>
+      <c r="C1946">
+        <v>-2.2492999999999999</v>
+      </c>
+    </row>
+    <row r="1947" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1947" s="1">
+        <v>45984</v>
+      </c>
+      <c r="B1947">
+        <v>5395.49</v>
+      </c>
+      <c r="C1947">
+        <v>-2.2492999999999999</v>
+      </c>
+    </row>
+    <row r="1948" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1948" s="1">
+        <v>45985</v>
+      </c>
+      <c r="B1948">
+        <v>5545.56</v>
+      </c>
+      <c r="C1948">
+        <v>-2.2107999999999999</v>
+      </c>
+    </row>
+    <row r="1949" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1949" s="1">
+        <v>45986</v>
+      </c>
+      <c r="B1949">
+        <v>5612.03</v>
+      </c>
+      <c r="C1949">
+        <v>-2.177</v>
+      </c>
+    </row>
+    <row r="1950" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1950" s="1">
+        <v>45987</v>
+      </c>
+      <c r="B1950">
+        <v>5618.36</v>
+      </c>
+      <c r="C1950">
+        <v>-2.1551</v>
+      </c>
+    </row>
+    <row r="1951" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1951" s="1">
+        <v>45988</v>
+      </c>
+      <c r="B1951">
+        <v>5598.05</v>
+      </c>
+      <c r="C1951">
+        <v>-2.1471</v>
+      </c>
+    </row>
+    <row r="1952" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1952" s="1">
+        <v>45989</v>
+      </c>
+      <c r="B1952">
+        <v>5599.11</v>
+      </c>
+      <c r="C1952">
+        <v>-2.1812000000000005</v>
+      </c>
+    </row>
+    <row r="1953" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1953" s="1">
+        <v>45990</v>
+      </c>
+      <c r="B1953">
+        <v>5599.11</v>
+      </c>
+      <c r="C1953">
+        <v>-2.1812000000000005</v>
+      </c>
+    </row>
+    <row r="1954" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1954" s="1">
+        <v>45991</v>
+      </c>
+      <c r="B1954">
+        <v>5599.11</v>
+      </c>
+      <c r="C1954">
+        <v>-2.1812000000000005</v>
+      </c>
+    </row>
+    <row r="1955" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1955" s="1">
+        <v>45992</v>
+      </c>
+      <c r="B1955">
+        <v>5644.76</v>
+      </c>
+      <c r="C1955">
+        <v>-2.2565</v>
+      </c>
+    </row>
+    <row r="1956" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1956" s="1">
+        <v>45993</v>
+      </c>
+      <c r="B1956">
+        <v>5624.04</v>
+      </c>
+      <c r="C1956">
+        <v>-2.2495000000000003</v>
+      </c>
+    </row>
+    <row r="1957" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1957" s="1">
+        <v>45994</v>
+      </c>
+      <c r="B1957">
+        <v>5534.92</v>
+      </c>
+      <c r="C1957">
+        <v>-2.2233000000000001</v>
+      </c>
+    </row>
+    <row r="1958" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1958" s="1">
+        <v>45995</v>
+      </c>
+      <c r="B1958">
+        <v>5615.43</v>
+      </c>
+      <c r="C1958">
+        <v>-2.2410999999999994</v>
+      </c>
+    </row>
+    <row r="1959" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1959" s="1">
+        <v>45996</v>
+      </c>
+      <c r="B1959">
+        <v>5662.46</v>
+      </c>
+      <c r="C1959">
+        <v>-2.3021000000000003</v>
+      </c>
+    </row>
+    <row r="1960" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1960" s="1">
+        <v>45997</v>
+      </c>
+      <c r="B1960">
+        <v>5662.46</v>
+      </c>
+      <c r="C1960">
+        <v>-2.3021000000000003</v>
+      </c>
+    </row>
+    <row r="1961" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1961" s="1">
+        <v>45998</v>
+      </c>
+      <c r="B1961">
+        <v>5662.46</v>
+      </c>
+      <c r="C1961">
+        <v>-2.3021000000000003</v>
+      </c>
+    </row>
+    <row r="1962" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1962" s="1">
+        <v>45999</v>
+      </c>
+      <c r="B1962">
+        <v>5662.55</v>
+      </c>
+      <c r="C1962">
+        <v>-2.3252999999999999</v>
+      </c>
+    </row>
+    <row r="1963" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1963" s="1">
+        <v>46000</v>
+      </c>
+      <c r="B1963">
+        <v>5554.68</v>
+      </c>
+      <c r="C1963">
+        <v>-2.3517999999999999</v>
+      </c>
+    </row>
+    <row r="1964" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1964" s="1">
+        <v>46001</v>
+      </c>
+      <c r="B1964">
+        <v>5581.1</v>
+      </c>
+      <c r="C1964">
+        <v>-2.3087999999999997</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -21332,28 +22032,28 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C44AB31A-70CE-4A6E-A84E-7592026AAEFA}">
-  <dimension ref="A1:E1899"/>
+  <dimension ref="A1:E1963"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="0" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="3" max="4" width="9.140625" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="5" max="5" width="9.140625" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" cm="1">
-        <f t="array" ref="A1:B1899">_xll.BDH("HSTECH Index", "PX_LAST", "7/27/2020", "10/7/2025", "Days", "C", "BEST_FPERIOD_OVERRIDE", "1BF")</f>
+        <f t="array" ref="A1:B1963">_xll.BDH("HSTECH Index", "PX_LAST", "7/27/2020", "12/10/2025", "Days", "C", "BEST_FPERIOD_OVERRIDE", "1BF")</f>
         <v>44039</v>
       </c>
       <c r="B1">
         <v>6774.78</v>
       </c>
       <c r="C1" cm="1">
-        <f t="array" ref="C1:C1899">_xll.BDH("GCNY10YR Index", "PX_LAST", "7/27/2020", "10/7/2025", "Days", "C", "Dates", "Hide")</f>
+        <f t="array" ref="C1:C1963">_xll.BDH("GCNY10YR Index", "PX_LAST", "7/27/2020", "12/10/2025", "Days", "C", "Dates", "Hide")</f>
         <v>2.8959999999999999</v>
       </c>
       <c r="D1" cm="1">
-        <f t="array" ref="D1:D1899">_xll.BDH("USGG10YR Index", "PX_LAST", "7/27/2020", "10/7/2025", "Days", "C", "Dates", "Hide")</f>
+        <f t="array" ref="D1:D1963">_xll.BDH("USGG10YR Index", "PX_LAST", "7/27/2020", "12/10/2025", "Days", "C", "Dates", "Hide")</f>
         <v>0.61509999999999998</v>
       </c>
       <c r="E1">
@@ -54783,7 +55483,7 @@
         <v>4.2343000000000002</v>
       </c>
       <c r="E1858">
-        <f t="shared" ref="E1858:E1899" si="29">C1858-D1858</f>
+        <f t="shared" ref="E1858:E1921" si="29">C1858-D1858</f>
         <v>-2.4643000000000002</v>
       </c>
     </row>
@@ -55523,6 +56223,1158 @@
       <c r="E1899">
         <f t="shared" si="29"/>
         <v>-2.2520000000000002</v>
+      </c>
+    </row>
+    <row r="1900" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1900" s="1">
+        <v>45938</v>
+      </c>
+      <c r="B1900">
+        <v>6514.19</v>
+      </c>
+      <c r="C1900">
+        <v>1.871</v>
+      </c>
+      <c r="D1900">
+        <v>4.1170999999999998</v>
+      </c>
+      <c r="E1900">
+        <f t="shared" si="29"/>
+        <v>-2.2460999999999998</v>
+      </c>
+    </row>
+    <row r="1901" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1901" s="1">
+        <v>45939</v>
+      </c>
+      <c r="B1901">
+        <v>6471.34</v>
+      </c>
+      <c r="C1901">
+        <v>1.851</v>
+      </c>
+      <c r="D1901">
+        <v>4.1383999999999999</v>
+      </c>
+      <c r="E1901">
+        <f t="shared" si="29"/>
+        <v>-2.2873999999999999</v>
+      </c>
+    </row>
+    <row r="1902" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1902" s="1">
+        <v>45940</v>
+      </c>
+      <c r="B1902">
+        <v>6259.75</v>
+      </c>
+      <c r="C1902">
+        <v>1.8560000000000001</v>
+      </c>
+      <c r="D1902">
+        <v>4.0321999999999996</v>
+      </c>
+      <c r="E1902">
+        <f t="shared" si="29"/>
+        <v>-2.1761999999999997</v>
+      </c>
+    </row>
+    <row r="1903" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1903" s="1">
+        <v>45941</v>
+      </c>
+      <c r="B1903">
+        <v>6259.75</v>
+      </c>
+      <c r="C1903">
+        <v>1.8560000000000001</v>
+      </c>
+      <c r="D1903">
+        <v>4.0321999999999996</v>
+      </c>
+      <c r="E1903">
+        <f t="shared" si="29"/>
+        <v>-2.1761999999999997</v>
+      </c>
+    </row>
+    <row r="1904" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1904" s="1">
+        <v>45942</v>
+      </c>
+      <c r="B1904">
+        <v>6259.75</v>
+      </c>
+      <c r="C1904">
+        <v>1.8560000000000001</v>
+      </c>
+      <c r="D1904">
+        <v>4.0321999999999996</v>
+      </c>
+      <c r="E1904">
+        <f t="shared" si="29"/>
+        <v>-2.1761999999999997</v>
+      </c>
+    </row>
+    <row r="1905" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1905" s="1">
+        <v>45943</v>
+      </c>
+      <c r="B1905">
+        <v>6145.51</v>
+      </c>
+      <c r="C1905">
+        <v>1.8480000000000001</v>
+      </c>
+      <c r="D1905">
+        <v>4.0321999999999996</v>
+      </c>
+      <c r="E1905">
+        <f t="shared" si="29"/>
+        <v>-2.1841999999999997</v>
+      </c>
+    </row>
+    <row r="1906" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1906" s="1">
+        <v>45944</v>
+      </c>
+      <c r="B1906">
+        <v>5923.26</v>
+      </c>
+      <c r="C1906">
+        <v>1.8380000000000001</v>
+      </c>
+      <c r="D1906">
+        <v>4.0320999999999998</v>
+      </c>
+      <c r="E1906">
+        <f t="shared" si="29"/>
+        <v>-2.1940999999999997</v>
+      </c>
+    </row>
+    <row r="1907" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1907" s="1">
+        <v>45945</v>
+      </c>
+      <c r="B1907">
+        <v>6075.27</v>
+      </c>
+      <c r="C1907">
+        <v>1.8440000000000001</v>
+      </c>
+      <c r="D1907">
+        <v>4.0282</v>
+      </c>
+      <c r="E1907">
+        <f t="shared" si="29"/>
+        <v>-2.1841999999999997</v>
+      </c>
+    </row>
+    <row r="1908" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1908" s="1">
+        <v>45946</v>
+      </c>
+      <c r="B1908">
+        <v>6003.56</v>
+      </c>
+      <c r="C1908">
+        <v>1.839</v>
+      </c>
+      <c r="D1908">
+        <v>3.9744999999999999</v>
+      </c>
+      <c r="E1908">
+        <f t="shared" si="29"/>
+        <v>-2.1355</v>
+      </c>
+    </row>
+    <row r="1909" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1909" s="1">
+        <v>45947</v>
+      </c>
+      <c r="B1909">
+        <v>5760.38</v>
+      </c>
+      <c r="C1909">
+        <v>1.827</v>
+      </c>
+      <c r="D1909">
+        <v>4.0087999999999999</v>
+      </c>
+      <c r="E1909">
+        <f t="shared" si="29"/>
+        <v>-2.1818</v>
+      </c>
+    </row>
+    <row r="1910" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1910" s="1">
+        <v>45948</v>
+      </c>
+      <c r="B1910">
+        <v>5760.38</v>
+      </c>
+      <c r="C1910">
+        <v>1.827</v>
+      </c>
+      <c r="D1910">
+        <v>4.0087999999999999</v>
+      </c>
+      <c r="E1910">
+        <f t="shared" si="29"/>
+        <v>-2.1818</v>
+      </c>
+    </row>
+    <row r="1911" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1911" s="1">
+        <v>45949</v>
+      </c>
+      <c r="B1911">
+        <v>5760.38</v>
+      </c>
+      <c r="C1911">
+        <v>1.827</v>
+      </c>
+      <c r="D1911">
+        <v>4.0087999999999999</v>
+      </c>
+      <c r="E1911">
+        <f t="shared" si="29"/>
+        <v>-2.1818</v>
+      </c>
+    </row>
+    <row r="1912" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1912" s="1">
+        <v>45950</v>
+      </c>
+      <c r="B1912">
+        <v>5933.17</v>
+      </c>
+      <c r="C1912">
+        <v>1.847</v>
+      </c>
+      <c r="D1912">
+        <v>3.98</v>
+      </c>
+      <c r="E1912">
+        <f t="shared" si="29"/>
+        <v>-2.133</v>
+      </c>
+    </row>
+    <row r="1913" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1913" s="1">
+        <v>45951</v>
+      </c>
+      <c r="B1913">
+        <v>6007.94</v>
+      </c>
+      <c r="C1913">
+        <v>1.839</v>
+      </c>
+      <c r="D1913">
+        <v>3.9626999999999999</v>
+      </c>
+      <c r="E1913">
+        <f t="shared" si="29"/>
+        <v>-2.1236999999999999</v>
+      </c>
+    </row>
+    <row r="1914" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1914" s="1">
+        <v>45952</v>
+      </c>
+      <c r="B1914">
+        <v>5923.09</v>
+      </c>
+      <c r="C1914">
+        <v>1.829</v>
+      </c>
+      <c r="D1914">
+        <v>3.9493</v>
+      </c>
+      <c r="E1914">
+        <f t="shared" si="29"/>
+        <v>-2.1203000000000003</v>
+      </c>
+    </row>
+    <row r="1915" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1915" s="1">
+        <v>45953</v>
+      </c>
+      <c r="B1915">
+        <v>5951.45</v>
+      </c>
+      <c r="C1915">
+        <v>1.837</v>
+      </c>
+      <c r="D1915">
+        <v>4.0008999999999997</v>
+      </c>
+      <c r="E1915">
+        <f t="shared" si="29"/>
+        <v>-2.1638999999999999</v>
+      </c>
+    </row>
+    <row r="1916" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1916" s="1">
+        <v>45954</v>
+      </c>
+      <c r="B1916">
+        <v>6059.89</v>
+      </c>
+      <c r="C1916">
+        <v>1.851</v>
+      </c>
+      <c r="D1916">
+        <v>4.0007000000000001</v>
+      </c>
+      <c r="E1916">
+        <f t="shared" si="29"/>
+        <v>-2.1497000000000002</v>
+      </c>
+    </row>
+    <row r="1917" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1917" s="1">
+        <v>45955</v>
+      </c>
+      <c r="B1917">
+        <v>6059.89</v>
+      </c>
+      <c r="C1917">
+        <v>1.851</v>
+      </c>
+      <c r="D1917">
+        <v>4.0007000000000001</v>
+      </c>
+      <c r="E1917">
+        <f t="shared" si="29"/>
+        <v>-2.1497000000000002</v>
+      </c>
+    </row>
+    <row r="1918" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1918" s="1">
+        <v>45956</v>
+      </c>
+      <c r="B1918">
+        <v>6059.89</v>
+      </c>
+      <c r="C1918">
+        <v>1.851</v>
+      </c>
+      <c r="D1918">
+        <v>4.0007000000000001</v>
+      </c>
+      <c r="E1918">
+        <f t="shared" si="29"/>
+        <v>-2.1497000000000002</v>
+      </c>
+    </row>
+    <row r="1919" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1919" s="1">
+        <v>45957</v>
+      </c>
+      <c r="B1919">
+        <v>6171.08</v>
+      </c>
+      <c r="C1919">
+        <v>1.81</v>
+      </c>
+      <c r="D1919">
+        <v>3.9794999999999998</v>
+      </c>
+      <c r="E1919">
+        <f t="shared" si="29"/>
+        <v>-2.1694999999999998</v>
+      </c>
+    </row>
+    <row r="1920" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1920" s="1">
+        <v>45958</v>
+      </c>
+      <c r="B1920">
+        <v>6093.44</v>
+      </c>
+      <c r="C1920">
+        <v>1.8129999999999999</v>
+      </c>
+      <c r="D1920">
+        <v>3.9756</v>
+      </c>
+      <c r="E1920">
+        <f t="shared" si="29"/>
+        <v>-2.1626000000000003</v>
+      </c>
+    </row>
+    <row r="1921" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1921" s="1">
+        <v>45959</v>
+      </c>
+      <c r="B1921">
+        <v>6093.44</v>
+      </c>
+      <c r="C1921">
+        <v>1.8140000000000001</v>
+      </c>
+      <c r="D1921">
+        <v>4.0757000000000003</v>
+      </c>
+      <c r="E1921">
+        <f t="shared" si="29"/>
+        <v>-2.2617000000000003</v>
+      </c>
+    </row>
+    <row r="1922" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1922" s="1">
+        <v>45960</v>
+      </c>
+      <c r="B1922">
+        <v>6051.76</v>
+      </c>
+      <c r="C1922">
+        <v>1.81</v>
+      </c>
+      <c r="D1922">
+        <v>4.0970000000000004</v>
+      </c>
+      <c r="E1922">
+        <f t="shared" ref="E1922:E1963" si="30">C1922-D1922</f>
+        <v>-2.2870000000000004</v>
+      </c>
+    </row>
+    <row r="1923" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1923" s="1">
+        <v>45961</v>
+      </c>
+      <c r="B1923">
+        <v>5908.08</v>
+      </c>
+      <c r="C1923">
+        <v>1.7969999999999999</v>
+      </c>
+      <c r="D1923">
+        <v>4.0774999999999997</v>
+      </c>
+      <c r="E1923">
+        <f t="shared" si="30"/>
+        <v>-2.2805</v>
+      </c>
+    </row>
+    <row r="1924" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1924" s="1">
+        <v>45962</v>
+      </c>
+      <c r="B1924">
+        <v>5908.08</v>
+      </c>
+      <c r="C1924">
+        <v>1.7969999999999999</v>
+      </c>
+      <c r="D1924">
+        <v>4.0774999999999997</v>
+      </c>
+      <c r="E1924">
+        <f t="shared" si="30"/>
+        <v>-2.2805</v>
+      </c>
+    </row>
+    <row r="1925" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1925" s="1">
+        <v>45963</v>
+      </c>
+      <c r="B1925">
+        <v>5908.08</v>
+      </c>
+      <c r="C1925">
+        <v>1.7969999999999999</v>
+      </c>
+      <c r="D1925">
+        <v>4.0774999999999997</v>
+      </c>
+      <c r="E1925">
+        <f t="shared" si="30"/>
+        <v>-2.2805</v>
+      </c>
+    </row>
+    <row r="1926" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1926" s="1">
+        <v>45964</v>
+      </c>
+      <c r="B1926">
+        <v>5922.48</v>
+      </c>
+      <c r="C1926">
+        <v>1.792</v>
+      </c>
+      <c r="D1926">
+        <v>4.1104000000000003</v>
+      </c>
+      <c r="E1926">
+        <f t="shared" si="30"/>
+        <v>-2.3184000000000005</v>
+      </c>
+    </row>
+    <row r="1927" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1927" s="1">
+        <v>45965</v>
+      </c>
+      <c r="B1927">
+        <v>5818.29</v>
+      </c>
+      <c r="C1927">
+        <v>1.7949999999999999</v>
+      </c>
+      <c r="D1927">
+        <v>4.0852000000000004</v>
+      </c>
+      <c r="E1927">
+        <f t="shared" si="30"/>
+        <v>-2.2902000000000005</v>
+      </c>
+    </row>
+    <row r="1928" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1928" s="1">
+        <v>45966</v>
+      </c>
+      <c r="B1928">
+        <v>5785.85</v>
+      </c>
+      <c r="C1928">
+        <v>1.7969999999999999</v>
+      </c>
+      <c r="D1928">
+        <v>4.1590999999999996</v>
+      </c>
+      <c r="E1928">
+        <f t="shared" si="30"/>
+        <v>-2.3620999999999999</v>
+      </c>
+    </row>
+    <row r="1929" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1929" s="1">
+        <v>45967</v>
+      </c>
+      <c r="B1929">
+        <v>5944.22</v>
+      </c>
+      <c r="C1929">
+        <v>1.806</v>
+      </c>
+      <c r="D1929">
+        <v>4.0831</v>
+      </c>
+      <c r="E1929">
+        <f t="shared" si="30"/>
+        <v>-2.2770999999999999</v>
+      </c>
+    </row>
+    <row r="1930" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1930" s="1">
+        <v>45968</v>
+      </c>
+      <c r="B1930">
+        <v>5837.36</v>
+      </c>
+      <c r="C1930">
+        <v>1.8080000000000001</v>
+      </c>
+      <c r="D1930">
+        <v>4.0965999999999996</v>
+      </c>
+      <c r="E1930">
+        <f t="shared" si="30"/>
+        <v>-2.2885999999999997</v>
+      </c>
+    </row>
+    <row r="1931" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1931" s="1">
+        <v>45969</v>
+      </c>
+      <c r="B1931">
+        <v>5837.36</v>
+      </c>
+      <c r="C1931">
+        <v>1.8080000000000001</v>
+      </c>
+      <c r="D1931">
+        <v>4.0965999999999996</v>
+      </c>
+      <c r="E1931">
+        <f t="shared" si="30"/>
+        <v>-2.2885999999999997</v>
+      </c>
+    </row>
+    <row r="1932" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1932" s="1">
+        <v>45970</v>
+      </c>
+      <c r="B1932">
+        <v>5837.36</v>
+      </c>
+      <c r="C1932">
+        <v>1.8080000000000001</v>
+      </c>
+      <c r="D1932">
+        <v>4.0965999999999996</v>
+      </c>
+      <c r="E1932">
+        <f t="shared" si="30"/>
+        <v>-2.2885999999999997</v>
+      </c>
+    </row>
+    <row r="1933" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1933" s="1">
+        <v>45971</v>
+      </c>
+      <c r="B1933">
+        <v>5915.56</v>
+      </c>
+      <c r="C1933">
+        <v>1.8080000000000001</v>
+      </c>
+      <c r="D1933">
+        <v>4.1159999999999997</v>
+      </c>
+      <c r="E1933">
+        <f t="shared" si="30"/>
+        <v>-2.3079999999999998</v>
+      </c>
+    </row>
+    <row r="1934" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1934" s="1">
+        <v>45972</v>
+      </c>
+      <c r="B1934">
+        <v>5924.39</v>
+      </c>
+      <c r="C1934">
+        <v>1.8109999999999999</v>
+      </c>
+      <c r="D1934">
+        <v>4.1159999999999997</v>
+      </c>
+      <c r="E1934">
+        <f t="shared" si="30"/>
+        <v>-2.3049999999999997</v>
+      </c>
+    </row>
+    <row r="1935" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1935" s="1">
+        <v>45973</v>
+      </c>
+      <c r="B1935">
+        <v>5933.99</v>
+      </c>
+      <c r="C1935">
+        <v>1.804</v>
+      </c>
+      <c r="D1935">
+        <v>4.0693000000000001</v>
+      </c>
+      <c r="E1935">
+        <f t="shared" si="30"/>
+        <v>-2.2652999999999999</v>
+      </c>
+    </row>
+    <row r="1936" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1936" s="1">
+        <v>45974</v>
+      </c>
+      <c r="B1936">
+        <v>5981.3</v>
+      </c>
+      <c r="C1936">
+        <v>1.8080000000000001</v>
+      </c>
+      <c r="D1936">
+        <v>4.1192000000000002</v>
+      </c>
+      <c r="E1936">
+        <f t="shared" si="30"/>
+        <v>-2.3112000000000004</v>
+      </c>
+    </row>
+    <row r="1937" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1937" s="1">
+        <v>45975</v>
+      </c>
+      <c r="B1937">
+        <v>5812.8</v>
+      </c>
+      <c r="C1937">
+        <v>1.8080000000000001</v>
+      </c>
+      <c r="D1937">
+        <v>4.1482999999999999</v>
+      </c>
+      <c r="E1937">
+        <f t="shared" si="30"/>
+        <v>-2.3403</v>
+      </c>
+    </row>
+    <row r="1938" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1938" s="1">
+        <v>45976</v>
+      </c>
+      <c r="B1938">
+        <v>5812.8</v>
+      </c>
+      <c r="C1938">
+        <v>1.8080000000000001</v>
+      </c>
+      <c r="D1938">
+        <v>4.1482999999999999</v>
+      </c>
+      <c r="E1938">
+        <f t="shared" si="30"/>
+        <v>-2.3403</v>
+      </c>
+    </row>
+    <row r="1939" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1939" s="1">
+        <v>45977</v>
+      </c>
+      <c r="B1939">
+        <v>5812.8</v>
+      </c>
+      <c r="C1939">
+        <v>1.8080000000000001</v>
+      </c>
+      <c r="D1939">
+        <v>4.1482999999999999</v>
+      </c>
+      <c r="E1939">
+        <f t="shared" si="30"/>
+        <v>-2.3403</v>
+      </c>
+    </row>
+    <row r="1940" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1940" s="1">
+        <v>45978</v>
+      </c>
+      <c r="B1940">
+        <v>5756.88</v>
+      </c>
+      <c r="C1940">
+        <v>1.8069999999999999</v>
+      </c>
+      <c r="D1940">
+        <v>4.1386000000000003</v>
+      </c>
+      <c r="E1940">
+        <f t="shared" si="30"/>
+        <v>-2.3316000000000003</v>
+      </c>
+    </row>
+    <row r="1941" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1941" s="1">
+        <v>45979</v>
+      </c>
+      <c r="B1941">
+        <v>5645.73</v>
+      </c>
+      <c r="C1941">
+        <v>1.806</v>
+      </c>
+      <c r="D1941">
+        <v>4.1134000000000004</v>
+      </c>
+      <c r="E1941">
+        <f t="shared" si="30"/>
+        <v>-2.3074000000000003</v>
+      </c>
+    </row>
+    <row r="1942" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1942" s="1">
+        <v>45980</v>
+      </c>
+      <c r="B1942">
+        <v>5606.9</v>
+      </c>
+      <c r="C1942">
+        <v>1.81</v>
+      </c>
+      <c r="D1942">
+        <v>4.1367000000000003</v>
+      </c>
+      <c r="E1942">
+        <f t="shared" si="30"/>
+        <v>-2.3267000000000002</v>
+      </c>
+    </row>
+    <row r="1943" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1943" s="1">
+        <v>45981</v>
+      </c>
+      <c r="B1943">
+        <v>5574.59</v>
+      </c>
+      <c r="C1943">
+        <v>1.8109999999999999</v>
+      </c>
+      <c r="D1943">
+        <v>4.0845000000000002</v>
+      </c>
+      <c r="E1943">
+        <f t="shared" si="30"/>
+        <v>-2.2735000000000003</v>
+      </c>
+    </row>
+    <row r="1944" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1944" s="1">
+        <v>45982</v>
+      </c>
+      <c r="B1944">
+        <v>5395.49</v>
+      </c>
+      <c r="C1944">
+        <v>1.8140000000000001</v>
+      </c>
+      <c r="D1944">
+        <v>4.0632999999999999</v>
+      </c>
+      <c r="E1944">
+        <f t="shared" si="30"/>
+        <v>-2.2492999999999999</v>
+      </c>
+    </row>
+    <row r="1945" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1945" s="1">
+        <v>45983</v>
+      </c>
+      <c r="B1945">
+        <v>5395.49</v>
+      </c>
+      <c r="C1945">
+        <v>1.8140000000000001</v>
+      </c>
+      <c r="D1945">
+        <v>4.0632999999999999</v>
+      </c>
+      <c r="E1945">
+        <f t="shared" si="30"/>
+        <v>-2.2492999999999999</v>
+      </c>
+    </row>
+    <row r="1946" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1946" s="1">
+        <v>45984</v>
+      </c>
+      <c r="B1946">
+        <v>5395.49</v>
+      </c>
+      <c r="C1946">
+        <v>1.8140000000000001</v>
+      </c>
+      <c r="D1946">
+        <v>4.0632999999999999</v>
+      </c>
+      <c r="E1946">
+        <f t="shared" si="30"/>
+        <v>-2.2492999999999999</v>
+      </c>
+    </row>
+    <row r="1947" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1947" s="1">
+        <v>45985</v>
+      </c>
+      <c r="B1947">
+        <v>5545.56</v>
+      </c>
+      <c r="C1947">
+        <v>1.8140000000000001</v>
+      </c>
+      <c r="D1947">
+        <v>4.0247999999999999</v>
+      </c>
+      <c r="E1947">
+        <f t="shared" si="30"/>
+        <v>-2.2107999999999999</v>
+      </c>
+    </row>
+    <row r="1948" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1948" s="1">
+        <v>45986</v>
+      </c>
+      <c r="B1948">
+        <v>5612.03</v>
+      </c>
+      <c r="C1948">
+        <v>1.819</v>
+      </c>
+      <c r="D1948">
+        <v>3.996</v>
+      </c>
+      <c r="E1948">
+        <f t="shared" si="30"/>
+        <v>-2.177</v>
+      </c>
+    </row>
+    <row r="1949" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1949" s="1">
+        <v>45987</v>
+      </c>
+      <c r="B1949">
+        <v>5618.36</v>
+      </c>
+      <c r="C1949">
+        <v>1.839</v>
+      </c>
+      <c r="D1949">
+        <v>3.9941</v>
+      </c>
+      <c r="E1949">
+        <f t="shared" si="30"/>
+        <v>-2.1551</v>
+      </c>
+    </row>
+    <row r="1950" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1950" s="1">
+        <v>45988</v>
+      </c>
+      <c r="B1950">
+        <v>5598.05</v>
+      </c>
+      <c r="C1950">
+        <v>1.847</v>
+      </c>
+      <c r="D1950">
+        <v>3.9941</v>
+      </c>
+      <c r="E1950">
+        <f t="shared" si="30"/>
+        <v>-2.1471</v>
+      </c>
+    </row>
+    <row r="1951" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1951" s="1">
+        <v>45989</v>
+      </c>
+      <c r="B1951">
+        <v>5599.11</v>
+      </c>
+      <c r="C1951">
+        <v>1.8320000000000001</v>
+      </c>
+      <c r="D1951">
+        <v>4.0132000000000003</v>
+      </c>
+      <c r="E1951">
+        <f t="shared" si="30"/>
+        <v>-2.1812000000000005</v>
+      </c>
+    </row>
+    <row r="1952" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1952" s="1">
+        <v>45990</v>
+      </c>
+      <c r="B1952">
+        <v>5599.11</v>
+      </c>
+      <c r="C1952">
+        <v>1.8320000000000001</v>
+      </c>
+      <c r="D1952">
+        <v>4.0132000000000003</v>
+      </c>
+      <c r="E1952">
+        <f t="shared" si="30"/>
+        <v>-2.1812000000000005</v>
+      </c>
+    </row>
+    <row r="1953" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1953" s="1">
+        <v>45991</v>
+      </c>
+      <c r="B1953">
+        <v>5599.11</v>
+      </c>
+      <c r="C1953">
+        <v>1.8320000000000001</v>
+      </c>
+      <c r="D1953">
+        <v>4.0132000000000003</v>
+      </c>
+      <c r="E1953">
+        <f t="shared" si="30"/>
+        <v>-2.1812000000000005</v>
+      </c>
+    </row>
+    <row r="1954" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1954" s="1">
+        <v>45992</v>
+      </c>
+      <c r="B1954">
+        <v>5644.76</v>
+      </c>
+      <c r="C1954">
+        <v>1.83</v>
+      </c>
+      <c r="D1954">
+        <v>4.0865</v>
+      </c>
+      <c r="E1954">
+        <f t="shared" si="30"/>
+        <v>-2.2565</v>
+      </c>
+    </row>
+    <row r="1955" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1955" s="1">
+        <v>45993</v>
+      </c>
+      <c r="B1955">
+        <v>5624.04</v>
+      </c>
+      <c r="C1955">
+        <v>1.837</v>
+      </c>
+      <c r="D1955">
+        <v>4.0865</v>
+      </c>
+      <c r="E1955">
+        <f t="shared" si="30"/>
+        <v>-2.2495000000000003</v>
+      </c>
+    </row>
+    <row r="1956" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1956" s="1">
+        <v>45994</v>
+      </c>
+      <c r="B1956">
+        <v>5534.92</v>
+      </c>
+      <c r="C1956">
+        <v>1.84</v>
+      </c>
+      <c r="D1956">
+        <v>4.0632999999999999</v>
+      </c>
+      <c r="E1956">
+        <f t="shared" si="30"/>
+        <v>-2.2233000000000001</v>
+      </c>
+    </row>
+    <row r="1957" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1957" s="1">
+        <v>45995</v>
+      </c>
+      <c r="B1957">
+        <v>5615.43</v>
+      </c>
+      <c r="C1957">
+        <v>1.857</v>
+      </c>
+      <c r="D1957">
+        <v>4.0980999999999996</v>
+      </c>
+      <c r="E1957">
+        <f t="shared" si="30"/>
+        <v>-2.2410999999999994</v>
+      </c>
+    </row>
+    <row r="1958" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1958" s="1">
+        <v>45996</v>
+      </c>
+      <c r="B1958">
+        <v>5662.46</v>
+      </c>
+      <c r="C1958">
+        <v>1.833</v>
+      </c>
+      <c r="D1958">
+        <v>4.1351000000000004</v>
+      </c>
+      <c r="E1958">
+        <f t="shared" si="30"/>
+        <v>-2.3021000000000003</v>
+      </c>
+    </row>
+    <row r="1959" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1959" s="1">
+        <v>45997</v>
+      </c>
+      <c r="B1959">
+        <v>5662.46</v>
+      </c>
+      <c r="C1959">
+        <v>1.833</v>
+      </c>
+      <c r="D1959">
+        <v>4.1351000000000004</v>
+      </c>
+      <c r="E1959">
+        <f t="shared" si="30"/>
+        <v>-2.3021000000000003</v>
+      </c>
+    </row>
+    <row r="1960" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1960" s="1">
+        <v>45998</v>
+      </c>
+      <c r="B1960">
+        <v>5662.46</v>
+      </c>
+      <c r="C1960">
+        <v>1.833</v>
+      </c>
+      <c r="D1960">
+        <v>4.1351000000000004</v>
+      </c>
+      <c r="E1960">
+        <f t="shared" si="30"/>
+        <v>-2.3021000000000003</v>
+      </c>
+    </row>
+    <row r="1961" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1961" s="1">
+        <v>45999</v>
+      </c>
+      <c r="B1961">
+        <v>5662.55</v>
+      </c>
+      <c r="C1961">
+        <v>1.839</v>
+      </c>
+      <c r="D1961">
+        <v>4.1642999999999999</v>
+      </c>
+      <c r="E1961">
+        <f t="shared" si="30"/>
+        <v>-2.3252999999999999</v>
+      </c>
+    </row>
+    <row r="1962" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1962" s="1">
+        <v>46000</v>
+      </c>
+      <c r="B1962">
+        <v>5554.68</v>
+      </c>
+      <c r="C1962">
+        <v>1.8360000000000001</v>
+      </c>
+      <c r="D1962">
+        <v>4.1878000000000002</v>
+      </c>
+      <c r="E1962">
+        <f t="shared" si="30"/>
+        <v>-2.3517999999999999</v>
+      </c>
+    </row>
+    <row r="1963" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1963" s="1">
+        <v>46001</v>
+      </c>
+      <c r="B1963">
+        <v>5581.1</v>
+      </c>
+      <c r="C1963">
+        <v>1.8380000000000001</v>
+      </c>
+      <c r="D1963">
+        <v>4.1467999999999998</v>
+      </c>
+      <c r="E1963">
+        <f t="shared" si="30"/>
+        <v>-2.3087999999999997</v>
       </c>
     </row>
   </sheetData>

--- a/BOND_EQT/reg_HS Tech.xlsx
+++ b/BOND_EQT/reg_HS Tech.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c060ac0a7f9c7ae2/main/CRAMC_Desktop/EU/BOND_EQT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="51" documentId="8_{2773DC52-B2E1-442E-8E9F-479DDE4DEB2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92A0A9AD-D0EE-4E79-B964-F45C0E181E08}"/>
+  <xr:revisionPtr revIDLastSave="89" documentId="8_{2773DC52-B2E1-442E-8E9F-479DDE4DEB2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E1788EE-0ED7-4ADD-81F8-8B45B301AB72}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="480" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22050" yWindow="6960" windowWidth="13275" windowHeight="14640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -127,29 +127,33 @@
 <volTypes xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <volType type="realTimeData">
     <main first="bofaddin.rtdserver">
-      <tp t="s">
-        <v>#N/A N/A</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
-        <stp>BDH|10116834236230611777</stp>
+        <stp>BDH|16460447689170116789</stp>
         <tr r="C1" s="2"/>
-      </tp>
-      <tp t="s">
-        <v>#N/A N/A</v>
-        <stp/>
-        <stp>BDH|15235929736366660909</stp>
-        <tr r="D1" s="2"/>
       </tp>
     </main>
     <main first="bofaddin.rtdserver">
-      <tp t="s">
-        <v>#N/A N/A</v>
+      <tp t="b">
+        <v>0</v>
         <stp/>
-        <stp>BDH|9838886424443202136</stp>
+        <stp>BDH|1206982613596557044</stp>
         <tr r="A1" s="2"/>
+      </tp>
+      <tp t="b">
+        <v>0</v>
+        <stp/>
+        <stp>BDH|8301846746529412528</stp>
+        <tr r="D1" s="2"/>
       </tp>
     </main>
   </volType>
 </volTypes>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -415,14 +419,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C1964"/>
+  <dimension ref="A1:C2018"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -22023,6 +22027,600 @@
       </c>
       <c r="C1964">
         <v>-2.3087999999999997</v>
+      </c>
+    </row>
+    <row r="1965" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1965" s="1">
+        <v>46002</v>
+      </c>
+      <c r="B1965">
+        <v>5534.59</v>
+      </c>
+      <c r="C1965">
+        <v>-2.3346</v>
+      </c>
+    </row>
+    <row r="1966" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1966" s="1">
+        <v>46003</v>
+      </c>
+      <c r="B1966">
+        <v>5638.05</v>
+      </c>
+      <c r="C1966">
+        <v>-2.3420999999999998</v>
+      </c>
+    </row>
+    <row r="1967" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1967" s="1">
+        <v>46004</v>
+      </c>
+      <c r="B1967">
+        <v>5638.05</v>
+      </c>
+      <c r="C1967">
+        <v>-2.3420999999999998</v>
+      </c>
+    </row>
+    <row r="1968" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1968" s="1">
+        <v>46005</v>
+      </c>
+      <c r="B1968">
+        <v>5638.05</v>
+      </c>
+      <c r="C1968">
+        <v>-2.3420999999999998</v>
+      </c>
+    </row>
+    <row r="1969" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1969" s="1">
+        <v>46006</v>
+      </c>
+      <c r="B1969">
+        <v>5498.42</v>
+      </c>
+      <c r="C1969">
+        <v>-2.3163</v>
+      </c>
+    </row>
+    <row r="1970" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1970" s="1">
+        <v>46007</v>
+      </c>
+      <c r="B1970">
+        <v>5402.51</v>
+      </c>
+      <c r="C1970">
+        <v>-2.2929999999999993</v>
+      </c>
+    </row>
+    <row r="1971" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1971" s="1">
+        <v>46008</v>
+      </c>
+      <c r="B1971">
+        <v>5457.95</v>
+      </c>
+      <c r="C1971">
+        <v>-2.3167999999999997</v>
+      </c>
+    </row>
+    <row r="1972" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1972" s="1">
+        <v>46009</v>
+      </c>
+      <c r="B1972">
+        <v>5418.29</v>
+      </c>
+      <c r="C1972">
+        <v>-2.2856999999999994</v>
+      </c>
+    </row>
+    <row r="1973" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1973" s="1">
+        <v>46010</v>
+      </c>
+      <c r="B1973">
+        <v>5479.04</v>
+      </c>
+      <c r="C1973">
+        <v>-2.3190999999999997</v>
+      </c>
+    </row>
+    <row r="1974" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1974" s="1">
+        <v>46011</v>
+      </c>
+      <c r="B1974">
+        <v>5479.04</v>
+      </c>
+      <c r="C1974">
+        <v>-2.3190999999999997</v>
+      </c>
+    </row>
+    <row r="1975" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1975" s="1">
+        <v>46012</v>
+      </c>
+      <c r="B1975">
+        <v>5479.04</v>
+      </c>
+      <c r="C1975">
+        <v>-2.3190999999999997</v>
+      </c>
+    </row>
+    <row r="1976" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1976" s="1">
+        <v>46013</v>
+      </c>
+      <c r="B1976">
+        <v>5526.83</v>
+      </c>
+      <c r="C1976">
+        <v>-2.3228</v>
+      </c>
+    </row>
+    <row r="1977" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1977" s="1">
+        <v>46014</v>
+      </c>
+      <c r="B1977">
+        <v>5488.89</v>
+      </c>
+      <c r="C1977">
+        <v>-2.3237999999999999</v>
+      </c>
+    </row>
+    <row r="1978" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1978" s="1">
+        <v>46015</v>
+      </c>
+      <c r="B1978">
+        <v>5499.3</v>
+      </c>
+      <c r="C1978">
+        <v>-2.2934999999999999</v>
+      </c>
+    </row>
+    <row r="1979" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1979" s="1">
+        <v>46016</v>
+      </c>
+      <c r="B1979">
+        <v>5499.3</v>
+      </c>
+      <c r="C1979">
+        <v>-2.2954999999999997</v>
+      </c>
+    </row>
+    <row r="1980" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1980" s="1">
+        <v>46017</v>
+      </c>
+      <c r="B1980">
+        <v>5499.3</v>
+      </c>
+      <c r="C1980">
+        <v>-2.2927</v>
+      </c>
+    </row>
+    <row r="1981" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1981" s="1">
+        <v>46018</v>
+      </c>
+      <c r="B1981">
+        <v>5499.3</v>
+      </c>
+      <c r="C1981">
+        <v>-2.2927</v>
+      </c>
+    </row>
+    <row r="1982" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1982" s="1">
+        <v>46019</v>
+      </c>
+      <c r="B1982">
+        <v>5499.3</v>
+      </c>
+      <c r="C1982">
+        <v>-2.2927</v>
+      </c>
+    </row>
+    <row r="1983" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1983" s="1">
+        <v>46020</v>
+      </c>
+      <c r="B1983">
+        <v>5483.01</v>
+      </c>
+      <c r="C1983">
+        <v>-2.2521999999999998</v>
+      </c>
+    </row>
+    <row r="1984" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1984" s="1">
+        <v>46021</v>
+      </c>
+      <c r="B1984">
+        <v>5578.38</v>
+      </c>
+      <c r="C1984">
+        <v>-2.2659000000000002</v>
+      </c>
+    </row>
+    <row r="1985" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1985" s="1">
+        <v>46022</v>
+      </c>
+      <c r="B1985">
+        <v>5515.98</v>
+      </c>
+      <c r="C1985">
+        <v>-2.3119999999999998</v>
+      </c>
+    </row>
+    <row r="1986" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1986" s="1">
+        <v>46023</v>
+      </c>
+      <c r="B1986">
+        <v>5515.98</v>
+      </c>
+      <c r="C1986">
+        <v>-2.3119999999999998</v>
+      </c>
+    </row>
+    <row r="1987" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1987" s="1">
+        <v>46024</v>
+      </c>
+      <c r="B1987">
+        <v>5736.44</v>
+      </c>
+      <c r="C1987">
+        <v>-2.3356999999999997</v>
+      </c>
+    </row>
+    <row r="1988" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1988" s="1">
+        <v>46025</v>
+      </c>
+      <c r="B1988">
+        <v>5736.44</v>
+      </c>
+      <c r="C1988">
+        <v>-2.3356999999999997</v>
+      </c>
+    </row>
+    <row r="1989" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1989" s="1">
+        <v>46026</v>
+      </c>
+      <c r="B1989">
+        <v>5736.44</v>
+      </c>
+      <c r="C1989">
+        <v>-2.3356999999999997</v>
+      </c>
+    </row>
+    <row r="1990" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1990" s="1">
+        <v>46027</v>
+      </c>
+      <c r="B1990">
+        <v>5741.63</v>
+      </c>
+      <c r="C1990">
+        <v>-2.3052000000000001</v>
+      </c>
+    </row>
+    <row r="1991" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1991" s="1">
+        <v>46028</v>
+      </c>
+      <c r="B1991">
+        <v>5825.26</v>
+      </c>
+      <c r="C1991">
+        <v>-2.2910000000000004</v>
+      </c>
+    </row>
+    <row r="1992" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1992" s="1">
+        <v>46029</v>
+      </c>
+      <c r="B1992">
+        <v>5738.52</v>
+      </c>
+      <c r="C1992">
+        <v>-2.2504999999999997</v>
+      </c>
+    </row>
+    <row r="1993" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1993" s="1">
+        <v>46030</v>
+      </c>
+      <c r="B1993">
+        <v>5678.34</v>
+      </c>
+      <c r="C1993">
+        <v>-2.2812000000000001</v>
+      </c>
+    </row>
+    <row r="1994" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1994" s="1">
+        <v>46031</v>
+      </c>
+      <c r="B1994">
+        <v>5687.14</v>
+      </c>
+      <c r="C1994">
+        <v>-2.2933000000000003</v>
+      </c>
+    </row>
+    <row r="1995" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1995" s="1">
+        <v>46032</v>
+      </c>
+      <c r="B1995">
+        <v>5687.14</v>
+      </c>
+      <c r="C1995">
+        <v>-2.2933000000000003</v>
+      </c>
+    </row>
+    <row r="1996" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1996" s="1">
+        <v>46033</v>
+      </c>
+      <c r="B1996">
+        <v>5687.14</v>
+      </c>
+      <c r="C1996">
+        <v>-2.2933000000000003</v>
+      </c>
+    </row>
+    <row r="1997" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1997" s="1">
+        <v>46034</v>
+      </c>
+      <c r="B1997">
+        <v>5863.2</v>
+      </c>
+      <c r="C1997">
+        <v>-2.3122000000000003</v>
+      </c>
+    </row>
+    <row r="1998" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1998" s="1">
+        <v>46035</v>
+      </c>
+      <c r="B1998">
+        <v>5869.79</v>
+      </c>
+      <c r="C1998">
+        <v>-2.3241999999999998</v>
+      </c>
+    </row>
+    <row r="1999" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1999" s="1">
+        <v>46036</v>
+      </c>
+      <c r="B1999">
+        <v>5908.26</v>
+      </c>
+      <c r="C1999">
+        <v>-2.2829999999999995</v>
+      </c>
+    </row>
+    <row r="2000" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2000" s="1">
+        <v>46037</v>
+      </c>
+      <c r="B2000">
+        <v>5828.35</v>
+      </c>
+      <c r="C2000">
+        <v>-2.3204000000000002</v>
+      </c>
+    </row>
+    <row r="2001" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2001" s="1">
+        <v>46038</v>
+      </c>
+      <c r="B2001">
+        <v>5822.18</v>
+      </c>
+      <c r="C2001">
+        <v>-2.3818999999999999</v>
+      </c>
+    </row>
+    <row r="2002" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2002" s="1">
+        <v>46039</v>
+      </c>
+      <c r="B2002">
+        <v>5822.18</v>
+      </c>
+      <c r="C2002">
+        <v>-2.3818999999999999</v>
+      </c>
+    </row>
+    <row r="2003" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2003" s="1">
+        <v>46040</v>
+      </c>
+      <c r="B2003">
+        <v>5822.18</v>
+      </c>
+      <c r="C2003">
+        <v>-2.3818999999999999</v>
+      </c>
+    </row>
+    <row r="2004" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2004" s="1">
+        <v>46041</v>
+      </c>
+      <c r="B2004">
+        <v>5749.98</v>
+      </c>
+      <c r="C2004">
+        <v>-2.3849</v>
+      </c>
+    </row>
+    <row r="2005" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2005" s="1">
+        <v>46042</v>
+      </c>
+      <c r="B2005">
+        <v>5683.44</v>
+      </c>
+      <c r="C2005">
+        <v>-2.4525000000000006</v>
+      </c>
+    </row>
+    <row r="2006" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2006" s="1">
+        <v>46043</v>
+      </c>
+      <c r="B2006">
+        <v>5746.3</v>
+      </c>
+      <c r="C2006">
+        <v>-2.4108000000000001</v>
+      </c>
+    </row>
+    <row r="2007" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2007" s="1">
+        <v>46044</v>
+      </c>
+      <c r="B2007">
+        <v>5762.44</v>
+      </c>
+      <c r="C2007">
+        <v>-2.4099000000000004</v>
+      </c>
+    </row>
+    <row r="2008" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2008" s="1">
+        <v>46045</v>
+      </c>
+      <c r="B2008">
+        <v>5798.01</v>
+      </c>
+      <c r="C2008">
+        <v>-2.3971999999999998</v>
+      </c>
+    </row>
+    <row r="2009" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2009" s="1">
+        <v>46046</v>
+      </c>
+      <c r="B2009">
+        <v>5798.01</v>
+      </c>
+      <c r="C2009">
+        <v>-2.3971999999999998</v>
+      </c>
+    </row>
+    <row r="2010" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2010" s="1">
+        <v>46047</v>
+      </c>
+      <c r="B2010">
+        <v>5798.01</v>
+      </c>
+      <c r="C2010">
+        <v>-2.3971999999999998</v>
+      </c>
+    </row>
+    <row r="2011" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2011" s="1">
+        <v>46048</v>
+      </c>
+      <c r="B2011">
+        <v>5725.99</v>
+      </c>
+      <c r="C2011">
+        <v>-2.3872999999999998</v>
+      </c>
+    </row>
+    <row r="2012" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2012" s="1">
+        <v>46049</v>
+      </c>
+      <c r="B2012">
+        <v>5754.72</v>
+      </c>
+      <c r="C2012">
+        <v>-2.4131999999999998</v>
+      </c>
+    </row>
+    <row r="2013" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2013" s="1">
+        <v>46050</v>
+      </c>
+      <c r="B2013">
+        <v>5900.16</v>
+      </c>
+      <c r="C2013">
+        <v>-2.4241999999999999</v>
+      </c>
+    </row>
+    <row r="2014" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2014" s="1">
+        <v>46051</v>
+      </c>
+      <c r="B2014">
+        <v>5841.1</v>
+      </c>
+      <c r="C2014">
+        <v>-2.4153000000000002</v>
+      </c>
+    </row>
+    <row r="2015" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2015" s="1">
+        <v>46052</v>
+      </c>
+      <c r="B2015">
+        <v>5718.18</v>
+      </c>
+      <c r="C2015">
+        <v>-2.4245000000000001</v>
+      </c>
+    </row>
+    <row r="2016" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2016" s="1">
+        <v>46053</v>
+      </c>
+      <c r="B2016">
+        <v>5718.18</v>
+      </c>
+      <c r="C2016">
+        <v>-2.4245000000000001</v>
+      </c>
+    </row>
+    <row r="2017" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2017" s="1">
+        <v>46054</v>
+      </c>
+      <c r="B2017">
+        <v>5718.18</v>
+      </c>
+      <c r="C2017">
+        <v>-2.4245000000000001</v>
+      </c>
+    </row>
+    <row r="2018" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2018" s="1">
+        <v>46055</v>
+      </c>
+      <c r="B2018">
+        <v>5526.31</v>
+      </c>
+      <c r="C2018">
+        <v>-2.4584000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -22032,7 +22630,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C44AB31A-70CE-4A6E-A84E-7592026AAEFA}">
-  <dimension ref="A1:E1963"/>
+  <dimension ref="A1:E2017"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -22042,18 +22640,18 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" cm="1">
-        <f t="array" ref="A1:B1963">_xll.BDH("HSTECH Index", "PX_LAST", "7/27/2020", "12/10/2025", "Days", "C", "BEST_FPERIOD_OVERRIDE", "1BF")</f>
+        <f t="array" ref="A1:B2017">_xll.BDH("HSTECH Index", "PX_LAST", "7/27/2020", "2/2/2026", "Days", "C", "BEST_FPERIOD_OVERRIDE", "1BF")</f>
         <v>44039</v>
       </c>
       <c r="B1">
         <v>6774.78</v>
       </c>
       <c r="C1" cm="1">
-        <f t="array" ref="C1:C1963">_xll.BDH("GCNY10YR Index", "PX_LAST", "7/27/2020", "12/10/2025", "Days", "C", "Dates", "Hide")</f>
+        <f t="array" ref="C1:C2017">_xll.BDH("GCNY10YR Index", "PX_LAST", "7/27/2020", "2/2/2026", "Days", "C", "Dates", "Hide")</f>
         <v>2.8959999999999999</v>
       </c>
       <c r="D1" cm="1">
-        <f t="array" ref="D1:D1963">_xll.BDH("USGG10YR Index", "PX_LAST", "7/27/2020", "12/10/2025", "Days", "C", "Dates", "Hide")</f>
+        <f t="array" ref="D1:D2017">_xll.BDH("USGG10YR Index", "PX_LAST", "7/27/2020", "2/2/2026", "Days", "C", "Dates", "Hide")</f>
         <v>0.61509999999999998</v>
       </c>
       <c r="E1">
@@ -56635,7 +57233,7 @@
         <v>4.0970000000000004</v>
       </c>
       <c r="E1922">
-        <f t="shared" ref="E1922:E1963" si="30">C1922-D1922</f>
+        <f t="shared" ref="E1922:E1985" si="30">C1922-D1922</f>
         <v>-2.2870000000000004</v>
       </c>
     </row>
@@ -57375,6 +57973,978 @@
       <c r="E1963">
         <f t="shared" si="30"/>
         <v>-2.3087999999999997</v>
+      </c>
+    </row>
+    <row r="1964" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1964" s="1">
+        <v>46002</v>
+      </c>
+      <c r="B1964">
+        <v>5534.59</v>
+      </c>
+      <c r="C1964">
+        <v>1.8220000000000001</v>
+      </c>
+      <c r="D1964">
+        <v>4.1566000000000001</v>
+      </c>
+      <c r="E1964">
+        <f t="shared" si="30"/>
+        <v>-2.3346</v>
+      </c>
+    </row>
+    <row r="1965" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1965" s="1">
+        <v>46003</v>
+      </c>
+      <c r="B1965">
+        <v>5638.05</v>
+      </c>
+      <c r="C1965">
+        <v>1.8420000000000001</v>
+      </c>
+      <c r="D1965">
+        <v>4.1840999999999999</v>
+      </c>
+      <c r="E1965">
+        <f t="shared" si="30"/>
+        <v>-2.3420999999999998</v>
+      </c>
+    </row>
+    <row r="1966" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1966" s="1">
+        <v>46004</v>
+      </c>
+      <c r="B1966">
+        <v>5638.05</v>
+      </c>
+      <c r="C1966">
+        <v>1.8420000000000001</v>
+      </c>
+      <c r="D1966">
+        <v>4.1840999999999999</v>
+      </c>
+      <c r="E1966">
+        <f t="shared" si="30"/>
+        <v>-2.3420999999999998</v>
+      </c>
+    </row>
+    <row r="1967" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1967" s="1">
+        <v>46005</v>
+      </c>
+      <c r="B1967">
+        <v>5638.05</v>
+      </c>
+      <c r="C1967">
+        <v>1.8420000000000001</v>
+      </c>
+      <c r="D1967">
+        <v>4.1840999999999999</v>
+      </c>
+      <c r="E1967">
+        <f t="shared" si="30"/>
+        <v>-2.3420999999999998</v>
+      </c>
+    </row>
+    <row r="1968" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1968" s="1">
+        <v>46006</v>
+      </c>
+      <c r="B1968">
+        <v>5498.42</v>
+      </c>
+      <c r="C1968">
+        <v>1.8560000000000001</v>
+      </c>
+      <c r="D1968">
+        <v>4.1722999999999999</v>
+      </c>
+      <c r="E1968">
+        <f t="shared" si="30"/>
+        <v>-2.3163</v>
+      </c>
+    </row>
+    <row r="1969" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1969" s="1">
+        <v>46007</v>
+      </c>
+      <c r="B1969">
+        <v>5402.51</v>
+      </c>
+      <c r="C1969">
+        <v>1.8520000000000001</v>
+      </c>
+      <c r="D1969">
+        <v>4.1449999999999996</v>
+      </c>
+      <c r="E1969">
+        <f t="shared" si="30"/>
+        <v>-2.2929999999999993</v>
+      </c>
+    </row>
+    <row r="1970" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1970" s="1">
+        <v>46008</v>
+      </c>
+      <c r="B1970">
+        <v>5457.95</v>
+      </c>
+      <c r="C1970">
+        <v>1.8360000000000001</v>
+      </c>
+      <c r="D1970">
+        <v>4.1528</v>
+      </c>
+      <c r="E1970">
+        <f t="shared" si="30"/>
+        <v>-2.3167999999999997</v>
+      </c>
+    </row>
+    <row r="1971" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1971" s="1">
+        <v>46009</v>
+      </c>
+      <c r="B1971">
+        <v>5418.29</v>
+      </c>
+      <c r="C1971">
+        <v>1.8360000000000001</v>
+      </c>
+      <c r="D1971">
+        <v>4.1216999999999997</v>
+      </c>
+      <c r="E1971">
+        <f t="shared" si="30"/>
+        <v>-2.2856999999999994</v>
+      </c>
+    </row>
+    <row r="1972" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1972" s="1">
+        <v>46010</v>
+      </c>
+      <c r="B1972">
+        <v>5479.04</v>
+      </c>
+      <c r="C1972">
+        <v>1.8280000000000001</v>
+      </c>
+      <c r="D1972">
+        <v>4.1471</v>
+      </c>
+      <c r="E1972">
+        <f t="shared" si="30"/>
+        <v>-2.3190999999999997</v>
+      </c>
+    </row>
+    <row r="1973" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1973" s="1">
+        <v>46011</v>
+      </c>
+      <c r="B1973">
+        <v>5479.04</v>
+      </c>
+      <c r="C1973">
+        <v>1.8280000000000001</v>
+      </c>
+      <c r="D1973">
+        <v>4.1471</v>
+      </c>
+      <c r="E1973">
+        <f t="shared" si="30"/>
+        <v>-2.3190999999999997</v>
+      </c>
+    </row>
+    <row r="1974" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1974" s="1">
+        <v>46012</v>
+      </c>
+      <c r="B1974">
+        <v>5479.04</v>
+      </c>
+      <c r="C1974">
+        <v>1.8280000000000001</v>
+      </c>
+      <c r="D1974">
+        <v>4.1471</v>
+      </c>
+      <c r="E1974">
+        <f t="shared" si="30"/>
+        <v>-2.3190999999999997</v>
+      </c>
+    </row>
+    <row r="1975" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1975" s="1">
+        <v>46013</v>
+      </c>
+      <c r="B1975">
+        <v>5526.83</v>
+      </c>
+      <c r="C1975">
+        <v>1.84</v>
+      </c>
+      <c r="D1975">
+        <v>4.1627999999999998</v>
+      </c>
+      <c r="E1975">
+        <f t="shared" si="30"/>
+        <v>-2.3228</v>
+      </c>
+    </row>
+    <row r="1976" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1976" s="1">
+        <v>46014</v>
+      </c>
+      <c r="B1976">
+        <v>5488.89</v>
+      </c>
+      <c r="C1976">
+        <v>1.839</v>
+      </c>
+      <c r="D1976">
+        <v>4.1627999999999998</v>
+      </c>
+      <c r="E1976">
+        <f t="shared" si="30"/>
+        <v>-2.3237999999999999</v>
+      </c>
+    </row>
+    <row r="1977" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1977" s="1">
+        <v>46015</v>
+      </c>
+      <c r="B1977">
+        <v>5499.3</v>
+      </c>
+      <c r="C1977">
+        <v>1.84</v>
+      </c>
+      <c r="D1977">
+        <v>4.1334999999999997</v>
+      </c>
+      <c r="E1977">
+        <f t="shared" si="30"/>
+        <v>-2.2934999999999999</v>
+      </c>
+    </row>
+    <row r="1978" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1978" s="1">
+        <v>46016</v>
+      </c>
+      <c r="B1978">
+        <v>5499.3</v>
+      </c>
+      <c r="C1978">
+        <v>1.8380000000000001</v>
+      </c>
+      <c r="D1978">
+        <v>4.1334999999999997</v>
+      </c>
+      <c r="E1978">
+        <f t="shared" si="30"/>
+        <v>-2.2954999999999997</v>
+      </c>
+    </row>
+    <row r="1979" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1979" s="1">
+        <v>46017</v>
+      </c>
+      <c r="B1979">
+        <v>5499.3</v>
+      </c>
+      <c r="C1979">
+        <v>1.835</v>
+      </c>
+      <c r="D1979">
+        <v>4.1276999999999999</v>
+      </c>
+      <c r="E1979">
+        <f t="shared" si="30"/>
+        <v>-2.2927</v>
+      </c>
+    </row>
+    <row r="1980" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1980" s="1">
+        <v>46018</v>
+      </c>
+      <c r="B1980">
+        <v>5499.3</v>
+      </c>
+      <c r="C1980">
+        <v>1.835</v>
+      </c>
+      <c r="D1980">
+        <v>4.1276999999999999</v>
+      </c>
+      <c r="E1980">
+        <f t="shared" si="30"/>
+        <v>-2.2927</v>
+      </c>
+    </row>
+    <row r="1981" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1981" s="1">
+        <v>46019</v>
+      </c>
+      <c r="B1981">
+        <v>5499.3</v>
+      </c>
+      <c r="C1981">
+        <v>1.835</v>
+      </c>
+      <c r="D1981">
+        <v>4.1276999999999999</v>
+      </c>
+      <c r="E1981">
+        <f t="shared" si="30"/>
+        <v>-2.2927</v>
+      </c>
+    </row>
+    <row r="1982" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1982" s="1">
+        <v>46020</v>
+      </c>
+      <c r="B1982">
+        <v>5483.01</v>
+      </c>
+      <c r="C1982">
+        <v>1.8580000000000001</v>
+      </c>
+      <c r="D1982">
+        <v>4.1101999999999999</v>
+      </c>
+      <c r="E1982">
+        <f t="shared" si="30"/>
+        <v>-2.2521999999999998</v>
+      </c>
+    </row>
+    <row r="1983" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1983" s="1">
+        <v>46021</v>
+      </c>
+      <c r="B1983">
+        <v>5578.38</v>
+      </c>
+      <c r="C1983">
+        <v>1.8560000000000001</v>
+      </c>
+      <c r="D1983">
+        <v>4.1219000000000001</v>
+      </c>
+      <c r="E1983">
+        <f t="shared" si="30"/>
+        <v>-2.2659000000000002</v>
+      </c>
+    </row>
+    <row r="1984" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1984" s="1">
+        <v>46022</v>
+      </c>
+      <c r="B1984">
+        <v>5515.98</v>
+      </c>
+      <c r="C1984">
+        <v>1.855</v>
+      </c>
+      <c r="D1984">
+        <v>4.1669999999999998</v>
+      </c>
+      <c r="E1984">
+        <f t="shared" si="30"/>
+        <v>-2.3119999999999998</v>
+      </c>
+    </row>
+    <row r="1985" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1985" s="1">
+        <v>46023</v>
+      </c>
+      <c r="B1985">
+        <v>5515.98</v>
+      </c>
+      <c r="C1985">
+        <v>1.855</v>
+      </c>
+      <c r="D1985">
+        <v>4.1669999999999998</v>
+      </c>
+      <c r="E1985">
+        <f t="shared" si="30"/>
+        <v>-2.3119999999999998</v>
+      </c>
+    </row>
+    <row r="1986" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1986" s="1">
+        <v>46024</v>
+      </c>
+      <c r="B1986">
+        <v>5736.44</v>
+      </c>
+      <c r="C1986">
+        <v>1.855</v>
+      </c>
+      <c r="D1986">
+        <v>4.1906999999999996</v>
+      </c>
+      <c r="E1986">
+        <f t="shared" ref="E1986:E2017" si="31">C1986-D1986</f>
+        <v>-2.3356999999999997</v>
+      </c>
+    </row>
+    <row r="1987" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1987" s="1">
+        <v>46025</v>
+      </c>
+      <c r="B1987">
+        <v>5736.44</v>
+      </c>
+      <c r="C1987">
+        <v>1.855</v>
+      </c>
+      <c r="D1987">
+        <v>4.1906999999999996</v>
+      </c>
+      <c r="E1987">
+        <f t="shared" si="31"/>
+        <v>-2.3356999999999997</v>
+      </c>
+    </row>
+    <row r="1988" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1988" s="1">
+        <v>46026</v>
+      </c>
+      <c r="B1988">
+        <v>5736.44</v>
+      </c>
+      <c r="C1988">
+        <v>1.855</v>
+      </c>
+      <c r="D1988">
+        <v>4.1906999999999996</v>
+      </c>
+      <c r="E1988">
+        <f t="shared" si="31"/>
+        <v>-2.3356999999999997</v>
+      </c>
+    </row>
+    <row r="1989" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1989" s="1">
+        <v>46027</v>
+      </c>
+      <c r="B1989">
+        <v>5741.63</v>
+      </c>
+      <c r="C1989">
+        <v>1.8560000000000001</v>
+      </c>
+      <c r="D1989">
+        <v>4.1612</v>
+      </c>
+      <c r="E1989">
+        <f t="shared" si="31"/>
+        <v>-2.3052000000000001</v>
+      </c>
+    </row>
+    <row r="1990" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1990" s="1">
+        <v>46028</v>
+      </c>
+      <c r="B1990">
+        <v>5825.26</v>
+      </c>
+      <c r="C1990">
+        <v>1.8819999999999999</v>
+      </c>
+      <c r="D1990">
+        <v>4.173</v>
+      </c>
+      <c r="E1990">
+        <f t="shared" si="31"/>
+        <v>-2.2910000000000004</v>
+      </c>
+    </row>
+    <row r="1991" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1991" s="1">
+        <v>46029</v>
+      </c>
+      <c r="B1991">
+        <v>5738.52</v>
+      </c>
+      <c r="C1991">
+        <v>1.897</v>
+      </c>
+      <c r="D1991">
+        <v>4.1475</v>
+      </c>
+      <c r="E1991">
+        <f t="shared" si="31"/>
+        <v>-2.2504999999999997</v>
+      </c>
+    </row>
+    <row r="1992" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1992" s="1">
+        <v>46030</v>
+      </c>
+      <c r="B1992">
+        <v>5678.34</v>
+      </c>
+      <c r="C1992">
+        <v>1.8859999999999999</v>
+      </c>
+      <c r="D1992">
+        <v>4.1672000000000002</v>
+      </c>
+      <c r="E1992">
+        <f t="shared" si="31"/>
+        <v>-2.2812000000000001</v>
+      </c>
+    </row>
+    <row r="1993" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1993" s="1">
+        <v>46031</v>
+      </c>
+      <c r="B1993">
+        <v>5687.14</v>
+      </c>
+      <c r="C1993">
+        <v>1.8720000000000001</v>
+      </c>
+      <c r="D1993">
+        <v>4.1653000000000002</v>
+      </c>
+      <c r="E1993">
+        <f t="shared" si="31"/>
+        <v>-2.2933000000000003</v>
+      </c>
+    </row>
+    <row r="1994" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1994" s="1">
+        <v>46032</v>
+      </c>
+      <c r="B1994">
+        <v>5687.14</v>
+      </c>
+      <c r="C1994">
+        <v>1.8720000000000001</v>
+      </c>
+      <c r="D1994">
+        <v>4.1653000000000002</v>
+      </c>
+      <c r="E1994">
+        <f t="shared" si="31"/>
+        <v>-2.2933000000000003</v>
+      </c>
+    </row>
+    <row r="1995" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1995" s="1">
+        <v>46033</v>
+      </c>
+      <c r="B1995">
+        <v>5687.14</v>
+      </c>
+      <c r="C1995">
+        <v>1.8720000000000001</v>
+      </c>
+      <c r="D1995">
+        <v>4.1653000000000002</v>
+      </c>
+      <c r="E1995">
+        <f t="shared" si="31"/>
+        <v>-2.2933000000000003</v>
+      </c>
+    </row>
+    <row r="1996" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1996" s="1">
+        <v>46034</v>
+      </c>
+      <c r="B1996">
+        <v>5863.2</v>
+      </c>
+      <c r="C1996">
+        <v>1.863</v>
+      </c>
+      <c r="D1996">
+        <v>4.1752000000000002</v>
+      </c>
+      <c r="E1996">
+        <f t="shared" si="31"/>
+        <v>-2.3122000000000003</v>
+      </c>
+    </row>
+    <row r="1997" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1997" s="1">
+        <v>46035</v>
+      </c>
+      <c r="B1997">
+        <v>5869.79</v>
+      </c>
+      <c r="C1997">
+        <v>1.855</v>
+      </c>
+      <c r="D1997">
+        <v>4.1791999999999998</v>
+      </c>
+      <c r="E1997">
+        <f t="shared" si="31"/>
+        <v>-2.3241999999999998</v>
+      </c>
+    </row>
+    <row r="1998" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1998" s="1">
+        <v>46036</v>
+      </c>
+      <c r="B1998">
+        <v>5908.26</v>
+      </c>
+      <c r="C1998">
+        <v>1.849</v>
+      </c>
+      <c r="D1998">
+        <v>4.1319999999999997</v>
+      </c>
+      <c r="E1998">
+        <f t="shared" si="31"/>
+        <v>-2.2829999999999995</v>
+      </c>
+    </row>
+    <row r="1999" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1999" s="1">
+        <v>46037</v>
+      </c>
+      <c r="B1999">
+        <v>5828.35</v>
+      </c>
+      <c r="C1999">
+        <v>1.849</v>
+      </c>
+      <c r="D1999">
+        <v>4.1694000000000004</v>
+      </c>
+      <c r="E1999">
+        <f t="shared" si="31"/>
+        <v>-2.3204000000000002</v>
+      </c>
+    </row>
+    <row r="2000" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2000" s="1">
+        <v>46038</v>
+      </c>
+      <c r="B2000">
+        <v>5822.18</v>
+      </c>
+      <c r="C2000">
+        <v>1.841</v>
+      </c>
+      <c r="D2000">
+        <v>4.2229000000000001</v>
+      </c>
+      <c r="E2000">
+        <f t="shared" si="31"/>
+        <v>-2.3818999999999999</v>
+      </c>
+    </row>
+    <row r="2001" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2001" s="1">
+        <v>46039</v>
+      </c>
+      <c r="B2001">
+        <v>5822.18</v>
+      </c>
+      <c r="C2001">
+        <v>1.841</v>
+      </c>
+      <c r="D2001">
+        <v>4.2229000000000001</v>
+      </c>
+      <c r="E2001">
+        <f t="shared" si="31"/>
+        <v>-2.3818999999999999</v>
+      </c>
+    </row>
+    <row r="2002" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2002" s="1">
+        <v>46040</v>
+      </c>
+      <c r="B2002">
+        <v>5822.18</v>
+      </c>
+      <c r="C2002">
+        <v>1.841</v>
+      </c>
+      <c r="D2002">
+        <v>4.2229000000000001</v>
+      </c>
+      <c r="E2002">
+        <f t="shared" si="31"/>
+        <v>-2.3818999999999999</v>
+      </c>
+    </row>
+    <row r="2003" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2003" s="1">
+        <v>46041</v>
+      </c>
+      <c r="B2003">
+        <v>5749.98</v>
+      </c>
+      <c r="C2003">
+        <v>1.8380000000000001</v>
+      </c>
+      <c r="D2003">
+        <v>4.2229000000000001</v>
+      </c>
+      <c r="E2003">
+        <f t="shared" si="31"/>
+        <v>-2.3849</v>
+      </c>
+    </row>
+    <row r="2004" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2004" s="1">
+        <v>46042</v>
+      </c>
+      <c r="B2004">
+        <v>5683.44</v>
+      </c>
+      <c r="C2004">
+        <v>1.84</v>
+      </c>
+      <c r="D2004">
+        <v>4.2925000000000004</v>
+      </c>
+      <c r="E2004">
+        <f t="shared" si="31"/>
+        <v>-2.4525000000000006</v>
+      </c>
+    </row>
+    <row r="2005" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2005" s="1">
+        <v>46043</v>
+      </c>
+      <c r="B2005">
+        <v>5746.3</v>
+      </c>
+      <c r="C2005">
+        <v>1.8320000000000001</v>
+      </c>
+      <c r="D2005">
+        <v>4.2427999999999999</v>
+      </c>
+      <c r="E2005">
+        <f t="shared" si="31"/>
+        <v>-2.4108000000000001</v>
+      </c>
+    </row>
+    <row r="2006" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2006" s="1">
+        <v>46044</v>
+      </c>
+      <c r="B2006">
+        <v>5762.44</v>
+      </c>
+      <c r="C2006">
+        <v>1.835</v>
+      </c>
+      <c r="D2006">
+        <v>4.2449000000000003</v>
+      </c>
+      <c r="E2006">
+        <f t="shared" si="31"/>
+        <v>-2.4099000000000004</v>
+      </c>
+    </row>
+    <row r="2007" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2007" s="1">
+        <v>46045</v>
+      </c>
+      <c r="B2007">
+        <v>5798.01</v>
+      </c>
+      <c r="C2007">
+        <v>1.8280000000000001</v>
+      </c>
+      <c r="D2007">
+        <v>4.2252000000000001</v>
+      </c>
+      <c r="E2007">
+        <f t="shared" si="31"/>
+        <v>-2.3971999999999998</v>
+      </c>
+    </row>
+    <row r="2008" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2008" s="1">
+        <v>46046</v>
+      </c>
+      <c r="B2008">
+        <v>5798.01</v>
+      </c>
+      <c r="C2008">
+        <v>1.8280000000000001</v>
+      </c>
+      <c r="D2008">
+        <v>4.2252000000000001</v>
+      </c>
+      <c r="E2008">
+        <f t="shared" si="31"/>
+        <v>-2.3971999999999998</v>
+      </c>
+    </row>
+    <row r="2009" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2009" s="1">
+        <v>46047</v>
+      </c>
+      <c r="B2009">
+        <v>5798.01</v>
+      </c>
+      <c r="C2009">
+        <v>1.8280000000000001</v>
+      </c>
+      <c r="D2009">
+        <v>4.2252000000000001</v>
+      </c>
+      <c r="E2009">
+        <f t="shared" si="31"/>
+        <v>-2.3971999999999998</v>
+      </c>
+    </row>
+    <row r="2010" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2010" s="1">
+        <v>46048</v>
+      </c>
+      <c r="B2010">
+        <v>5725.99</v>
+      </c>
+      <c r="C2010">
+        <v>1.8240000000000001</v>
+      </c>
+      <c r="D2010">
+        <v>4.2112999999999996</v>
+      </c>
+      <c r="E2010">
+        <f t="shared" si="31"/>
+        <v>-2.3872999999999998</v>
+      </c>
+    </row>
+    <row r="2011" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2011" s="1">
+        <v>46049</v>
+      </c>
+      <c r="B2011">
+        <v>5754.72</v>
+      </c>
+      <c r="C2011">
+        <v>1.83</v>
+      </c>
+      <c r="D2011">
+        <v>4.2431999999999999</v>
+      </c>
+      <c r="E2011">
+        <f t="shared" si="31"/>
+        <v>-2.4131999999999998</v>
+      </c>
+    </row>
+    <row r="2012" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2012" s="1">
+        <v>46050</v>
+      </c>
+      <c r="B2012">
+        <v>5900.16</v>
+      </c>
+      <c r="C2012">
+        <v>1.819</v>
+      </c>
+      <c r="D2012">
+        <v>4.2431999999999999</v>
+      </c>
+      <c r="E2012">
+        <f t="shared" si="31"/>
+        <v>-2.4241999999999999</v>
+      </c>
+    </row>
+    <row r="2013" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2013" s="1">
+        <v>46051</v>
+      </c>
+      <c r="B2013">
+        <v>5841.1</v>
+      </c>
+      <c r="C2013">
+        <v>1.8160000000000001</v>
+      </c>
+      <c r="D2013">
+        <v>4.2313000000000001</v>
+      </c>
+      <c r="E2013">
+        <f t="shared" si="31"/>
+        <v>-2.4153000000000002</v>
+      </c>
+    </row>
+    <row r="2014" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2014" s="1">
+        <v>46052</v>
+      </c>
+      <c r="B2014">
+        <v>5718.18</v>
+      </c>
+      <c r="C2014">
+        <v>1.8109999999999999</v>
+      </c>
+      <c r="D2014">
+        <v>4.2355</v>
+      </c>
+      <c r="E2014">
+        <f t="shared" si="31"/>
+        <v>-2.4245000000000001</v>
+      </c>
+    </row>
+    <row r="2015" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2015" s="1">
+        <v>46053</v>
+      </c>
+      <c r="B2015">
+        <v>5718.18</v>
+      </c>
+      <c r="C2015">
+        <v>1.8109999999999999</v>
+      </c>
+      <c r="D2015">
+        <v>4.2355</v>
+      </c>
+      <c r="E2015">
+        <f t="shared" si="31"/>
+        <v>-2.4245000000000001</v>
+      </c>
+    </row>
+    <row r="2016" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2016" s="1">
+        <v>46054</v>
+      </c>
+      <c r="B2016">
+        <v>5718.18</v>
+      </c>
+      <c r="C2016">
+        <v>1.8109999999999999</v>
+      </c>
+      <c r="D2016">
+        <v>4.2355</v>
+      </c>
+      <c r="E2016">
+        <f t="shared" si="31"/>
+        <v>-2.4245000000000001</v>
+      </c>
+    </row>
+    <row r="2017" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2017" s="1">
+        <v>46055</v>
+      </c>
+      <c r="B2017">
+        <v>5526.31</v>
+      </c>
+      <c r="C2017">
+        <v>1.819</v>
+      </c>
+      <c r="D2017">
+        <v>4.2774000000000001</v>
+      </c>
+      <c r="E2017">
+        <f t="shared" si="31"/>
+        <v>-2.4584000000000001</v>
       </c>
     </row>
   </sheetData>
